--- a/docs/CUFIC_WTS_데이터셋_제작양식.xlsx
+++ b/docs/CUFIC_WTS_데이터셋_제작양식.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재무제표" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="힌트" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시황" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="등락률(자동)" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -881,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1670,6 +1671,370 @@
         <v>588100</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1681,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P107"/>
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7875,7 +8240,2988 @@
         <v/>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="7"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="7"/>
+      <c r="G108" s="7"/>
+      <c r="H108" s="7"/>
+      <c r="I108" s="7"/>
+      <c r="J108" s="11">
+        <f>IF(C108="","",C108+D108)</f>
+      </c>
+      <c r="K108" s="11">
+        <f>IF(E108="","",E108+F108)</f>
+      </c>
+      <c r="L108" s="11">
+        <f>IF(J108="","",J108-K108)</f>
+      </c>
+      <c r="M108" s="11">
+        <f>IF(G108="","",G108-H108)</f>
+      </c>
+      <c r="N108" s="11">
+        <f>IF(M108="","",M108-I108)</f>
+      </c>
+      <c r="O108" s="11">
+        <f>IF(OR(L108="",L108&lt;=0),"자본잠식",ROUND(K108/L108*100,1))</f>
+      </c>
+      <c r="P108" s="11">
+        <f>IF(OR(L108="",L108&lt;=0),"—",ROUND(N108/L108*100,1))</f>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7"/>
+      <c r="B109" s="7"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
+      <c r="H109" s="7"/>
+      <c r="I109" s="7"/>
+      <c r="J109" s="11">
+        <f>IF(C109="","",C109+D109)</f>
+      </c>
+      <c r="K109" s="11">
+        <f>IF(E109="","",E109+F109)</f>
+      </c>
+      <c r="L109" s="11">
+        <f>IF(J109="","",J109-K109)</f>
+      </c>
+      <c r="M109" s="11">
+        <f>IF(G109="","",G109-H109)</f>
+      </c>
+      <c r="N109" s="11">
+        <f>IF(M109="","",M109-I109)</f>
+      </c>
+      <c r="O109" s="11">
+        <f>IF(OR(L109="",L109&lt;=0),"자본잠식",ROUND(K109/L109*100,1))</f>
+      </c>
+      <c r="P109" s="11">
+        <f>IF(OR(L109="",L109&lt;=0),"—",ROUND(N109/L109*100,1))</f>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+      <c r="G110" s="7"/>
+      <c r="H110" s="7"/>
+      <c r="I110" s="7"/>
+      <c r="J110" s="11">
+        <f>IF(C110="","",C110+D110)</f>
+      </c>
+      <c r="K110" s="11">
+        <f>IF(E110="","",E110+F110)</f>
+      </c>
+      <c r="L110" s="11">
+        <f>IF(J110="","",J110-K110)</f>
+      </c>
+      <c r="M110" s="11">
+        <f>IF(G110="","",G110-H110)</f>
+      </c>
+      <c r="N110" s="11">
+        <f>IF(M110="","",M110-I110)</f>
+      </c>
+      <c r="O110" s="11">
+        <f>IF(OR(L110="",L110&lt;=0),"자본잠식",ROUND(K110/L110*100,1))</f>
+      </c>
+      <c r="P110" s="11">
+        <f>IF(OR(L110="",L110&lt;=0),"—",ROUND(N110/L110*100,1))</f>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7"/>
+      <c r="B111" s="7"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="7"/>
+      <c r="H111" s="7"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="11">
+        <f>IF(C111="","",C111+D111)</f>
+      </c>
+      <c r="K111" s="11">
+        <f>IF(E111="","",E111+F111)</f>
+      </c>
+      <c r="L111" s="11">
+        <f>IF(J111="","",J111-K111)</f>
+      </c>
+      <c r="M111" s="11">
+        <f>IF(G111="","",G111-H111)</f>
+      </c>
+      <c r="N111" s="11">
+        <f>IF(M111="","",M111-I111)</f>
+      </c>
+      <c r="O111" s="11">
+        <f>IF(OR(L111="",L111&lt;=0),"자본잠식",ROUND(K111/L111*100,1))</f>
+      </c>
+      <c r="P111" s="11">
+        <f>IF(OR(L111="",L111&lt;=0),"—",ROUND(N111/L111*100,1))</f>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7"/>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="7"/>
+      <c r="J112" s="11">
+        <f>IF(C112="","",C112+D112)</f>
+      </c>
+      <c r="K112" s="11">
+        <f>IF(E112="","",E112+F112)</f>
+      </c>
+      <c r="L112" s="11">
+        <f>IF(J112="","",J112-K112)</f>
+      </c>
+      <c r="M112" s="11">
+        <f>IF(G112="","",G112-H112)</f>
+      </c>
+      <c r="N112" s="11">
+        <f>IF(M112="","",M112-I112)</f>
+      </c>
+      <c r="O112" s="11">
+        <f>IF(OR(L112="",L112&lt;=0),"자본잠식",ROUND(K112/L112*100,1))</f>
+      </c>
+      <c r="P112" s="11">
+        <f>IF(OR(L112="",L112&lt;=0),"—",ROUND(N112/L112*100,1))</f>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7"/>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="7"/>
+      <c r="J113" s="11">
+        <f>IF(C113="","",C113+D113)</f>
+      </c>
+      <c r="K113" s="11">
+        <f>IF(E113="","",E113+F113)</f>
+      </c>
+      <c r="L113" s="11">
+        <f>IF(J113="","",J113-K113)</f>
+      </c>
+      <c r="M113" s="11">
+        <f>IF(G113="","",G113-H113)</f>
+      </c>
+      <c r="N113" s="11">
+        <f>IF(M113="","",M113-I113)</f>
+      </c>
+      <c r="O113" s="11">
+        <f>IF(OR(L113="",L113&lt;=0),"자본잠식",ROUND(K113/L113*100,1))</f>
+      </c>
+      <c r="P113" s="11">
+        <f>IF(OR(L113="",L113&lt;=0),"—",ROUND(N113/L113*100,1))</f>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7"/>
+      <c r="B114" s="7"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="7"/>
+      <c r="J114" s="11">
+        <f>IF(C114="","",C114+D114)</f>
+      </c>
+      <c r="K114" s="11">
+        <f>IF(E114="","",E114+F114)</f>
+      </c>
+      <c r="L114" s="11">
+        <f>IF(J114="","",J114-K114)</f>
+      </c>
+      <c r="M114" s="11">
+        <f>IF(G114="","",G114-H114)</f>
+      </c>
+      <c r="N114" s="11">
+        <f>IF(M114="","",M114-I114)</f>
+      </c>
+      <c r="O114" s="11">
+        <f>IF(OR(L114="",L114&lt;=0),"자본잠식",ROUND(K114/L114*100,1))</f>
+      </c>
+      <c r="P114" s="11">
+        <f>IF(OR(L114="",L114&lt;=0),"—",ROUND(N114/L114*100,1))</f>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7"/>
+      <c r="B115" s="7"/>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="7"/>
+      <c r="J115" s="11">
+        <f>IF(C115="","",C115+D115)</f>
+      </c>
+      <c r="K115" s="11">
+        <f>IF(E115="","",E115+F115)</f>
+      </c>
+      <c r="L115" s="11">
+        <f>IF(J115="","",J115-K115)</f>
+      </c>
+      <c r="M115" s="11">
+        <f>IF(G115="","",G115-H115)</f>
+      </c>
+      <c r="N115" s="11">
+        <f>IF(M115="","",M115-I115)</f>
+      </c>
+      <c r="O115" s="11">
+        <f>IF(OR(L115="",L115&lt;=0),"자본잠식",ROUND(K115/L115*100,1))</f>
+      </c>
+      <c r="P115" s="11">
+        <f>IF(OR(L115="",L115&lt;=0),"—",ROUND(N115/L115*100,1))</f>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
+      <c r="F116" s="7"/>
+      <c r="G116" s="7"/>
+      <c r="H116" s="7"/>
+      <c r="I116" s="7"/>
+      <c r="J116" s="11">
+        <f>IF(C116="","",C116+D116)</f>
+      </c>
+      <c r="K116" s="11">
+        <f>IF(E116="","",E116+F116)</f>
+      </c>
+      <c r="L116" s="11">
+        <f>IF(J116="","",J116-K116)</f>
+      </c>
+      <c r="M116" s="11">
+        <f>IF(G116="","",G116-H116)</f>
+      </c>
+      <c r="N116" s="11">
+        <f>IF(M116="","",M116-I116)</f>
+      </c>
+      <c r="O116" s="11">
+        <f>IF(OR(L116="",L116&lt;=0),"자본잠식",ROUND(K116/L116*100,1))</f>
+      </c>
+      <c r="P116" s="11">
+        <f>IF(OR(L116="",L116&lt;=0),"—",ROUND(N116/L116*100,1))</f>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7"/>
+      <c r="B117" s="7"/>
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="7"/>
+      <c r="H117" s="7"/>
+      <c r="I117" s="7"/>
+      <c r="J117" s="11">
+        <f>IF(C117="","",C117+D117)</f>
+      </c>
+      <c r="K117" s="11">
+        <f>IF(E117="","",E117+F117)</f>
+      </c>
+      <c r="L117" s="11">
+        <f>IF(J117="","",J117-K117)</f>
+      </c>
+      <c r="M117" s="11">
+        <f>IF(G117="","",G117-H117)</f>
+      </c>
+      <c r="N117" s="11">
+        <f>IF(M117="","",M117-I117)</f>
+      </c>
+      <c r="O117" s="11">
+        <f>IF(OR(L117="",L117&lt;=0),"자본잠식",ROUND(K117/L117*100,1))</f>
+      </c>
+      <c r="P117" s="11">
+        <f>IF(OR(L117="",L117&lt;=0),"—",ROUND(N117/L117*100,1))</f>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7"/>
+      <c r="B118" s="7"/>
+      <c r="C118" s="7"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="7"/>
+      <c r="F118" s="7"/>
+      <c r="G118" s="7"/>
+      <c r="H118" s="7"/>
+      <c r="I118" s="7"/>
+      <c r="J118" s="11">
+        <f>IF(C118="","",C118+D118)</f>
+      </c>
+      <c r="K118" s="11">
+        <f>IF(E118="","",E118+F118)</f>
+      </c>
+      <c r="L118" s="11">
+        <f>IF(J118="","",J118-K118)</f>
+      </c>
+      <c r="M118" s="11">
+        <f>IF(G118="","",G118-H118)</f>
+      </c>
+      <c r="N118" s="11">
+        <f>IF(M118="","",M118-I118)</f>
+      </c>
+      <c r="O118" s="11">
+        <f>IF(OR(L118="",L118&lt;=0),"자본잠식",ROUND(K118/L118*100,1))</f>
+      </c>
+      <c r="P118" s="11">
+        <f>IF(OR(L118="",L118&lt;=0),"—",ROUND(N118/L118*100,1))</f>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7"/>
+      <c r="B119" s="7"/>
+      <c r="C119" s="7"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="7"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="7"/>
+      <c r="J119" s="11">
+        <f>IF(C119="","",C119+D119)</f>
+      </c>
+      <c r="K119" s="11">
+        <f>IF(E119="","",E119+F119)</f>
+      </c>
+      <c r="L119" s="11">
+        <f>IF(J119="","",J119-K119)</f>
+      </c>
+      <c r="M119" s="11">
+        <f>IF(G119="","",G119-H119)</f>
+      </c>
+      <c r="N119" s="11">
+        <f>IF(M119="","",M119-I119)</f>
+      </c>
+      <c r="O119" s="11">
+        <f>IF(OR(L119="",L119&lt;=0),"자본잠식",ROUND(K119/L119*100,1))</f>
+      </c>
+      <c r="P119" s="11">
+        <f>IF(OR(L119="",L119&lt;=0),"—",ROUND(N119/L119*100,1))</f>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7"/>
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="7"/>
+      <c r="H120" s="7"/>
+      <c r="I120" s="7"/>
+      <c r="J120" s="11">
+        <f>IF(C120="","",C120+D120)</f>
+      </c>
+      <c r="K120" s="11">
+        <f>IF(E120="","",E120+F120)</f>
+      </c>
+      <c r="L120" s="11">
+        <f>IF(J120="","",J120-K120)</f>
+      </c>
+      <c r="M120" s="11">
+        <f>IF(G120="","",G120-H120)</f>
+      </c>
+      <c r="N120" s="11">
+        <f>IF(M120="","",M120-I120)</f>
+      </c>
+      <c r="O120" s="11">
+        <f>IF(OR(L120="",L120&lt;=0),"자본잠식",ROUND(K120/L120*100,1))</f>
+      </c>
+      <c r="P120" s="11">
+        <f>IF(OR(L120="",L120&lt;=0),"—",ROUND(N120/L120*100,1))</f>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7"/>
+      <c r="B121" s="7"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="7"/>
+      <c r="J121" s="11">
+        <f>IF(C121="","",C121+D121)</f>
+      </c>
+      <c r="K121" s="11">
+        <f>IF(E121="","",E121+F121)</f>
+      </c>
+      <c r="L121" s="11">
+        <f>IF(J121="","",J121-K121)</f>
+      </c>
+      <c r="M121" s="11">
+        <f>IF(G121="","",G121-H121)</f>
+      </c>
+      <c r="N121" s="11">
+        <f>IF(M121="","",M121-I121)</f>
+      </c>
+      <c r="O121" s="11">
+        <f>IF(OR(L121="",L121&lt;=0),"자본잠식",ROUND(K121/L121*100,1))</f>
+      </c>
+      <c r="P121" s="11">
+        <f>IF(OR(L121="",L121&lt;=0),"—",ROUND(N121/L121*100,1))</f>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="7"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="7"/>
+      <c r="H122" s="7"/>
+      <c r="I122" s="7"/>
+      <c r="J122" s="11">
+        <f>IF(C122="","",C122+D122)</f>
+      </c>
+      <c r="K122" s="11">
+        <f>IF(E122="","",E122+F122)</f>
+      </c>
+      <c r="L122" s="11">
+        <f>IF(J122="","",J122-K122)</f>
+      </c>
+      <c r="M122" s="11">
+        <f>IF(G122="","",G122-H122)</f>
+      </c>
+      <c r="N122" s="11">
+        <f>IF(M122="","",M122-I122)</f>
+      </c>
+      <c r="O122" s="11">
+        <f>IF(OR(L122="",L122&lt;=0),"자본잠식",ROUND(K122/L122*100,1))</f>
+      </c>
+      <c r="P122" s="11">
+        <f>IF(OR(L122="",L122&lt;=0),"—",ROUND(N122/L122*100,1))</f>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7"/>
+      <c r="B123" s="7"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
+      <c r="G123" s="7"/>
+      <c r="H123" s="7"/>
+      <c r="I123" s="7"/>
+      <c r="J123" s="11">
+        <f>IF(C123="","",C123+D123)</f>
+      </c>
+      <c r="K123" s="11">
+        <f>IF(E123="","",E123+F123)</f>
+      </c>
+      <c r="L123" s="11">
+        <f>IF(J123="","",J123-K123)</f>
+      </c>
+      <c r="M123" s="11">
+        <f>IF(G123="","",G123-H123)</f>
+      </c>
+      <c r="N123" s="11">
+        <f>IF(M123="","",M123-I123)</f>
+      </c>
+      <c r="O123" s="11">
+        <f>IF(OR(L123="",L123&lt;=0),"자본잠식",ROUND(K123/L123*100,1))</f>
+      </c>
+      <c r="P123" s="11">
+        <f>IF(OR(L123="",L123&lt;=0),"—",ROUND(N123/L123*100,1))</f>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
+      <c r="G124" s="7"/>
+      <c r="H124" s="7"/>
+      <c r="I124" s="7"/>
+      <c r="J124" s="11">
+        <f>IF(C124="","",C124+D124)</f>
+      </c>
+      <c r="K124" s="11">
+        <f>IF(E124="","",E124+F124)</f>
+      </c>
+      <c r="L124" s="11">
+        <f>IF(J124="","",J124-K124)</f>
+      </c>
+      <c r="M124" s="11">
+        <f>IF(G124="","",G124-H124)</f>
+      </c>
+      <c r="N124" s="11">
+        <f>IF(M124="","",M124-I124)</f>
+      </c>
+      <c r="O124" s="11">
+        <f>IF(OR(L124="",L124&lt;=0),"자본잠식",ROUND(K124/L124*100,1))</f>
+      </c>
+      <c r="P124" s="11">
+        <f>IF(OR(L124="",L124&lt;=0),"—",ROUND(N124/L124*100,1))</f>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7"/>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="7"/>
+      <c r="H125" s="7"/>
+      <c r="I125" s="7"/>
+      <c r="J125" s="11">
+        <f>IF(C125="","",C125+D125)</f>
+      </c>
+      <c r="K125" s="11">
+        <f>IF(E125="","",E125+F125)</f>
+      </c>
+      <c r="L125" s="11">
+        <f>IF(J125="","",J125-K125)</f>
+      </c>
+      <c r="M125" s="11">
+        <f>IF(G125="","",G125-H125)</f>
+      </c>
+      <c r="N125" s="11">
+        <f>IF(M125="","",M125-I125)</f>
+      </c>
+      <c r="O125" s="11">
+        <f>IF(OR(L125="",L125&lt;=0),"자본잠식",ROUND(K125/L125*100,1))</f>
+      </c>
+      <c r="P125" s="11">
+        <f>IF(OR(L125="",L125&lt;=0),"—",ROUND(N125/L125*100,1))</f>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7"/>
+      <c r="B126" s="7"/>
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
+      <c r="I126" s="7"/>
+      <c r="J126" s="11">
+        <f>IF(C126="","",C126+D126)</f>
+      </c>
+      <c r="K126" s="11">
+        <f>IF(E126="","",E126+F126)</f>
+      </c>
+      <c r="L126" s="11">
+        <f>IF(J126="","",J126-K126)</f>
+      </c>
+      <c r="M126" s="11">
+        <f>IF(G126="","",G126-H126)</f>
+      </c>
+      <c r="N126" s="11">
+        <f>IF(M126="","",M126-I126)</f>
+      </c>
+      <c r="O126" s="11">
+        <f>IF(OR(L126="",L126&lt;=0),"자본잠식",ROUND(K126/L126*100,1))</f>
+      </c>
+      <c r="P126" s="11">
+        <f>IF(OR(L126="",L126&lt;=0),"—",ROUND(N126/L126*100,1))</f>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7"/>
+      <c r="B127" s="7"/>
+      <c r="C127" s="7"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
+      <c r="F127" s="7"/>
+      <c r="G127" s="7"/>
+      <c r="H127" s="7"/>
+      <c r="I127" s="7"/>
+      <c r="J127" s="11">
+        <f>IF(C127="","",C127+D127)</f>
+      </c>
+      <c r="K127" s="11">
+        <f>IF(E127="","",E127+F127)</f>
+      </c>
+      <c r="L127" s="11">
+        <f>IF(J127="","",J127-K127)</f>
+      </c>
+      <c r="M127" s="11">
+        <f>IF(G127="","",G127-H127)</f>
+      </c>
+      <c r="N127" s="11">
+        <f>IF(M127="","",M127-I127)</f>
+      </c>
+      <c r="O127" s="11">
+        <f>IF(OR(L127="",L127&lt;=0),"자본잠식",ROUND(K127/L127*100,1))</f>
+      </c>
+      <c r="P127" s="11">
+        <f>IF(OR(L127="",L127&lt;=0),"—",ROUND(N127/L127*100,1))</f>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7"/>
+      <c r="B128" s="7"/>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
+      <c r="F128" s="7"/>
+      <c r="G128" s="7"/>
+      <c r="H128" s="7"/>
+      <c r="I128" s="7"/>
+      <c r="J128" s="11">
+        <f>IF(C128="","",C128+D128)</f>
+      </c>
+      <c r="K128" s="11">
+        <f>IF(E128="","",E128+F128)</f>
+      </c>
+      <c r="L128" s="11">
+        <f>IF(J128="","",J128-K128)</f>
+      </c>
+      <c r="M128" s="11">
+        <f>IF(G128="","",G128-H128)</f>
+      </c>
+      <c r="N128" s="11">
+        <f>IF(M128="","",M128-I128)</f>
+      </c>
+      <c r="O128" s="11">
+        <f>IF(OR(L128="",L128&lt;=0),"자본잠식",ROUND(K128/L128*100,1))</f>
+      </c>
+      <c r="P128" s="11">
+        <f>IF(OR(L128="",L128&lt;=0),"—",ROUND(N128/L128*100,1))</f>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7"/>
+      <c r="B129" s="7"/>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
+      <c r="G129" s="7"/>
+      <c r="H129" s="7"/>
+      <c r="I129" s="7"/>
+      <c r="J129" s="11">
+        <f>IF(C129="","",C129+D129)</f>
+      </c>
+      <c r="K129" s="11">
+        <f>IF(E129="","",E129+F129)</f>
+      </c>
+      <c r="L129" s="11">
+        <f>IF(J129="","",J129-K129)</f>
+      </c>
+      <c r="M129" s="11">
+        <f>IF(G129="","",G129-H129)</f>
+      </c>
+      <c r="N129" s="11">
+        <f>IF(M129="","",M129-I129)</f>
+      </c>
+      <c r="O129" s="11">
+        <f>IF(OR(L129="",L129&lt;=0),"자본잠식",ROUND(K129/L129*100,1))</f>
+      </c>
+      <c r="P129" s="11">
+        <f>IF(OR(L129="",L129&lt;=0),"—",ROUND(N129/L129*100,1))</f>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7"/>
+      <c r="B130" s="7"/>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="7"/>
+      <c r="G130" s="7"/>
+      <c r="H130" s="7"/>
+      <c r="I130" s="7"/>
+      <c r="J130" s="11">
+        <f>IF(C130="","",C130+D130)</f>
+      </c>
+      <c r="K130" s="11">
+        <f>IF(E130="","",E130+F130)</f>
+      </c>
+      <c r="L130" s="11">
+        <f>IF(J130="","",J130-K130)</f>
+      </c>
+      <c r="M130" s="11">
+        <f>IF(G130="","",G130-H130)</f>
+      </c>
+      <c r="N130" s="11">
+        <f>IF(M130="","",M130-I130)</f>
+      </c>
+      <c r="O130" s="11">
+        <f>IF(OR(L130="",L130&lt;=0),"자본잠식",ROUND(K130/L130*100,1))</f>
+      </c>
+      <c r="P130" s="11">
+        <f>IF(OR(L130="",L130&lt;=0),"—",ROUND(N130/L130*100,1))</f>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7"/>
+      <c r="B131" s="7"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7"/>
+      <c r="G131" s="7"/>
+      <c r="H131" s="7"/>
+      <c r="I131" s="7"/>
+      <c r="J131" s="11">
+        <f>IF(C131="","",C131+D131)</f>
+      </c>
+      <c r="K131" s="11">
+        <f>IF(E131="","",E131+F131)</f>
+      </c>
+      <c r="L131" s="11">
+        <f>IF(J131="","",J131-K131)</f>
+      </c>
+      <c r="M131" s="11">
+        <f>IF(G131="","",G131-H131)</f>
+      </c>
+      <c r="N131" s="11">
+        <f>IF(M131="","",M131-I131)</f>
+      </c>
+      <c r="O131" s="11">
+        <f>IF(OR(L131="",L131&lt;=0),"자본잠식",ROUND(K131/L131*100,1))</f>
+      </c>
+      <c r="P131" s="11">
+        <f>IF(OR(L131="",L131&lt;=0),"—",ROUND(N131/L131*100,1))</f>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7"/>
+      <c r="B132" s="7"/>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7"/>
+      <c r="G132" s="7"/>
+      <c r="H132" s="7"/>
+      <c r="I132" s="7"/>
+      <c r="J132" s="11">
+        <f>IF(C132="","",C132+D132)</f>
+      </c>
+      <c r="K132" s="11">
+        <f>IF(E132="","",E132+F132)</f>
+      </c>
+      <c r="L132" s="11">
+        <f>IF(J132="","",J132-K132)</f>
+      </c>
+      <c r="M132" s="11">
+        <f>IF(G132="","",G132-H132)</f>
+      </c>
+      <c r="N132" s="11">
+        <f>IF(M132="","",M132-I132)</f>
+      </c>
+      <c r="O132" s="11">
+        <f>IF(OR(L132="",L132&lt;=0),"자본잠식",ROUND(K132/L132*100,1))</f>
+      </c>
+      <c r="P132" s="11">
+        <f>IF(OR(L132="",L132&lt;=0),"—",ROUND(N132/L132*100,1))</f>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="7"/>
+      <c r="H133" s="7"/>
+      <c r="I133" s="7"/>
+      <c r="J133" s="11">
+        <f>IF(C133="","",C133+D133)</f>
+      </c>
+      <c r="K133" s="11">
+        <f>IF(E133="","",E133+F133)</f>
+      </c>
+      <c r="L133" s="11">
+        <f>IF(J133="","",J133-K133)</f>
+      </c>
+      <c r="M133" s="11">
+        <f>IF(G133="","",G133-H133)</f>
+      </c>
+      <c r="N133" s="11">
+        <f>IF(M133="","",M133-I133)</f>
+      </c>
+      <c r="O133" s="11">
+        <f>IF(OR(L133="",L133&lt;=0),"자본잠식",ROUND(K133/L133*100,1))</f>
+      </c>
+      <c r="P133" s="11">
+        <f>IF(OR(L133="",L133&lt;=0),"—",ROUND(N133/L133*100,1))</f>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7"/>
+      <c r="B134" s="7"/>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
+      <c r="I134" s="7"/>
+      <c r="J134" s="11">
+        <f>IF(C134="","",C134+D134)</f>
+      </c>
+      <c r="K134" s="11">
+        <f>IF(E134="","",E134+F134)</f>
+      </c>
+      <c r="L134" s="11">
+        <f>IF(J134="","",J134-K134)</f>
+      </c>
+      <c r="M134" s="11">
+        <f>IF(G134="","",G134-H134)</f>
+      </c>
+      <c r="N134" s="11">
+        <f>IF(M134="","",M134-I134)</f>
+      </c>
+      <c r="O134" s="11">
+        <f>IF(OR(L134="",L134&lt;=0),"자본잠식",ROUND(K134/L134*100,1))</f>
+      </c>
+      <c r="P134" s="11">
+        <f>IF(OR(L134="",L134&lt;=0),"—",ROUND(N134/L134*100,1))</f>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7"/>
+      <c r="B135" s="7"/>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7"/>
+      <c r="G135" s="7"/>
+      <c r="H135" s="7"/>
+      <c r="I135" s="7"/>
+      <c r="J135" s="11">
+        <f>IF(C135="","",C135+D135)</f>
+      </c>
+      <c r="K135" s="11">
+        <f>IF(E135="","",E135+F135)</f>
+      </c>
+      <c r="L135" s="11">
+        <f>IF(J135="","",J135-K135)</f>
+      </c>
+      <c r="M135" s="11">
+        <f>IF(G135="","",G135-H135)</f>
+      </c>
+      <c r="N135" s="11">
+        <f>IF(M135="","",M135-I135)</f>
+      </c>
+      <c r="O135" s="11">
+        <f>IF(OR(L135="",L135&lt;=0),"자본잠식",ROUND(K135/L135*100,1))</f>
+      </c>
+      <c r="P135" s="11">
+        <f>IF(OR(L135="",L135&lt;=0),"—",ROUND(N135/L135*100,1))</f>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7"/>
+      <c r="B136" s="7"/>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7"/>
+      <c r="G136" s="7"/>
+      <c r="H136" s="7"/>
+      <c r="I136" s="7"/>
+      <c r="J136" s="11">
+        <f>IF(C136="","",C136+D136)</f>
+      </c>
+      <c r="K136" s="11">
+        <f>IF(E136="","",E136+F136)</f>
+      </c>
+      <c r="L136" s="11">
+        <f>IF(J136="","",J136-K136)</f>
+      </c>
+      <c r="M136" s="11">
+        <f>IF(G136="","",G136-H136)</f>
+      </c>
+      <c r="N136" s="11">
+        <f>IF(M136="","",M136-I136)</f>
+      </c>
+      <c r="O136" s="11">
+        <f>IF(OR(L136="",L136&lt;=0),"자본잠식",ROUND(K136/L136*100,1))</f>
+      </c>
+      <c r="P136" s="11">
+        <f>IF(OR(L136="",L136&lt;=0),"—",ROUND(N136/L136*100,1))</f>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7"/>
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="7"/>
+      <c r="H137" s="7"/>
+      <c r="I137" s="7"/>
+      <c r="J137" s="11">
+        <f>IF(C137="","",C137+D137)</f>
+      </c>
+      <c r="K137" s="11">
+        <f>IF(E137="","",E137+F137)</f>
+      </c>
+      <c r="L137" s="11">
+        <f>IF(J137="","",J137-K137)</f>
+      </c>
+      <c r="M137" s="11">
+        <f>IF(G137="","",G137-H137)</f>
+      </c>
+      <c r="N137" s="11">
+        <f>IF(M137="","",M137-I137)</f>
+      </c>
+      <c r="O137" s="11">
+        <f>IF(OR(L137="",L137&lt;=0),"자본잠식",ROUND(K137/L137*100,1))</f>
+      </c>
+      <c r="P137" s="11">
+        <f>IF(OR(L137="",L137&lt;=0),"—",ROUND(N137/L137*100,1))</f>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7"/>
+      <c r="B138" s="7"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="7"/>
+      <c r="J138" s="11">
+        <f>IF(C138="","",C138+D138)</f>
+      </c>
+      <c r="K138" s="11">
+        <f>IF(E138="","",E138+F138)</f>
+      </c>
+      <c r="L138" s="11">
+        <f>IF(J138="","",J138-K138)</f>
+      </c>
+      <c r="M138" s="11">
+        <f>IF(G138="","",G138-H138)</f>
+      </c>
+      <c r="N138" s="11">
+        <f>IF(M138="","",M138-I138)</f>
+      </c>
+      <c r="O138" s="11">
+        <f>IF(OR(L138="",L138&lt;=0),"자본잠식",ROUND(K138/L138*100,1))</f>
+      </c>
+      <c r="P138" s="11">
+        <f>IF(OR(L138="",L138&lt;=0),"—",ROUND(N138/L138*100,1))</f>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7"/>
+      <c r="B139" s="7"/>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7"/>
+      <c r="G139" s="7"/>
+      <c r="H139" s="7"/>
+      <c r="I139" s="7"/>
+      <c r="J139" s="11">
+        <f>IF(C139="","",C139+D139)</f>
+      </c>
+      <c r="K139" s="11">
+        <f>IF(E139="","",E139+F139)</f>
+      </c>
+      <c r="L139" s="11">
+        <f>IF(J139="","",J139-K139)</f>
+      </c>
+      <c r="M139" s="11">
+        <f>IF(G139="","",G139-H139)</f>
+      </c>
+      <c r="N139" s="11">
+        <f>IF(M139="","",M139-I139)</f>
+      </c>
+      <c r="O139" s="11">
+        <f>IF(OR(L139="",L139&lt;=0),"자본잠식",ROUND(K139/L139*100,1))</f>
+      </c>
+      <c r="P139" s="11">
+        <f>IF(OR(L139="",L139&lt;=0),"—",ROUND(N139/L139*100,1))</f>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7"/>
+      <c r="B140" s="7"/>
+      <c r="C140" s="7"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="7"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7"/>
+      <c r="I140" s="7"/>
+      <c r="J140" s="11">
+        <f>IF(C140="","",C140+D140)</f>
+      </c>
+      <c r="K140" s="11">
+        <f>IF(E140="","",E140+F140)</f>
+      </c>
+      <c r="L140" s="11">
+        <f>IF(J140="","",J140-K140)</f>
+      </c>
+      <c r="M140" s="11">
+        <f>IF(G140="","",G140-H140)</f>
+      </c>
+      <c r="N140" s="11">
+        <f>IF(M140="","",M140-I140)</f>
+      </c>
+      <c r="O140" s="11">
+        <f>IF(OR(L140="",L140&lt;=0),"자본잠식",ROUND(K140/L140*100,1))</f>
+      </c>
+      <c r="P140" s="11">
+        <f>IF(OR(L140="",L140&lt;=0),"—",ROUND(N140/L140*100,1))</f>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7"/>
+      <c r="B141" s="7"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
+      <c r="G141" s="7"/>
+      <c r="H141" s="7"/>
+      <c r="I141" s="7"/>
+      <c r="J141" s="11">
+        <f>IF(C141="","",C141+D141)</f>
+      </c>
+      <c r="K141" s="11">
+        <f>IF(E141="","",E141+F141)</f>
+      </c>
+      <c r="L141" s="11">
+        <f>IF(J141="","",J141-K141)</f>
+      </c>
+      <c r="M141" s="11">
+        <f>IF(G141="","",G141-H141)</f>
+      </c>
+      <c r="N141" s="11">
+        <f>IF(M141="","",M141-I141)</f>
+      </c>
+      <c r="O141" s="11">
+        <f>IF(OR(L141="",L141&lt;=0),"자본잠식",ROUND(K141/L141*100,1))</f>
+      </c>
+      <c r="P141" s="11">
+        <f>IF(OR(L141="",L141&lt;=0),"—",ROUND(N141/L141*100,1))</f>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7"/>
+      <c r="B142" s="7"/>
+      <c r="C142" s="7"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="7"/>
+      <c r="H142" s="7"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="11">
+        <f>IF(C142="","",C142+D142)</f>
+      </c>
+      <c r="K142" s="11">
+        <f>IF(E142="","",E142+F142)</f>
+      </c>
+      <c r="L142" s="11">
+        <f>IF(J142="","",J142-K142)</f>
+      </c>
+      <c r="M142" s="11">
+        <f>IF(G142="","",G142-H142)</f>
+      </c>
+      <c r="N142" s="11">
+        <f>IF(M142="","",M142-I142)</f>
+      </c>
+      <c r="O142" s="11">
+        <f>IF(OR(L142="",L142&lt;=0),"자본잠식",ROUND(K142/L142*100,1))</f>
+      </c>
+      <c r="P142" s="11">
+        <f>IF(OR(L142="",L142&lt;=0),"—",ROUND(N142/L142*100,1))</f>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7"/>
+      <c r="B143" s="7"/>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="7"/>
+      <c r="G143" s="7"/>
+      <c r="H143" s="7"/>
+      <c r="I143" s="7"/>
+      <c r="J143" s="11">
+        <f>IF(C143="","",C143+D143)</f>
+      </c>
+      <c r="K143" s="11">
+        <f>IF(E143="","",E143+F143)</f>
+      </c>
+      <c r="L143" s="11">
+        <f>IF(J143="","",J143-K143)</f>
+      </c>
+      <c r="M143" s="11">
+        <f>IF(G143="","",G143-H143)</f>
+      </c>
+      <c r="N143" s="11">
+        <f>IF(M143="","",M143-I143)</f>
+      </c>
+      <c r="O143" s="11">
+        <f>IF(OR(L143="",L143&lt;=0),"자본잠식",ROUND(K143/L143*100,1))</f>
+      </c>
+      <c r="P143" s="11">
+        <f>IF(OR(L143="",L143&lt;=0),"—",ROUND(N143/L143*100,1))</f>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7"/>
+      <c r="B144" s="7"/>
+      <c r="C144" s="7"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="7"/>
+      <c r="F144" s="7"/>
+      <c r="G144" s="7"/>
+      <c r="H144" s="7"/>
+      <c r="I144" s="7"/>
+      <c r="J144" s="11">
+        <f>IF(C144="","",C144+D144)</f>
+      </c>
+      <c r="K144" s="11">
+        <f>IF(E144="","",E144+F144)</f>
+      </c>
+      <c r="L144" s="11">
+        <f>IF(J144="","",J144-K144)</f>
+      </c>
+      <c r="M144" s="11">
+        <f>IF(G144="","",G144-H144)</f>
+      </c>
+      <c r="N144" s="11">
+        <f>IF(M144="","",M144-I144)</f>
+      </c>
+      <c r="O144" s="11">
+        <f>IF(OR(L144="",L144&lt;=0),"자본잠식",ROUND(K144/L144*100,1))</f>
+      </c>
+      <c r="P144" s="11">
+        <f>IF(OR(L144="",L144&lt;=0),"—",ROUND(N144/L144*100,1))</f>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7"/>
+      <c r="B145" s="7"/>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7"/>
+      <c r="G145" s="7"/>
+      <c r="H145" s="7"/>
+      <c r="I145" s="7"/>
+      <c r="J145" s="11">
+        <f>IF(C145="","",C145+D145)</f>
+      </c>
+      <c r="K145" s="11">
+        <f>IF(E145="","",E145+F145)</f>
+      </c>
+      <c r="L145" s="11">
+        <f>IF(J145="","",J145-K145)</f>
+      </c>
+      <c r="M145" s="11">
+        <f>IF(G145="","",G145-H145)</f>
+      </c>
+      <c r="N145" s="11">
+        <f>IF(M145="","",M145-I145)</f>
+      </c>
+      <c r="O145" s="11">
+        <f>IF(OR(L145="",L145&lt;=0),"자본잠식",ROUND(K145/L145*100,1))</f>
+      </c>
+      <c r="P145" s="11">
+        <f>IF(OR(L145="",L145&lt;=0),"—",ROUND(N145/L145*100,1))</f>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7"/>
+      <c r="B146" s="7"/>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
+      <c r="I146" s="7"/>
+      <c r="J146" s="11">
+        <f>IF(C146="","",C146+D146)</f>
+      </c>
+      <c r="K146" s="11">
+        <f>IF(E146="","",E146+F146)</f>
+      </c>
+      <c r="L146" s="11">
+        <f>IF(J146="","",J146-K146)</f>
+      </c>
+      <c r="M146" s="11">
+        <f>IF(G146="","",G146-H146)</f>
+      </c>
+      <c r="N146" s="11">
+        <f>IF(M146="","",M146-I146)</f>
+      </c>
+      <c r="O146" s="11">
+        <f>IF(OR(L146="",L146&lt;=0),"자본잠식",ROUND(K146/L146*100,1))</f>
+      </c>
+      <c r="P146" s="11">
+        <f>IF(OR(L146="",L146&lt;=0),"—",ROUND(N146/L146*100,1))</f>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="7"/>
+      <c r="B147" s="7"/>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="7"/>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
+      <c r="I147" s="7"/>
+      <c r="J147" s="11">
+        <f>IF(C147="","",C147+D147)</f>
+      </c>
+      <c r="K147" s="11">
+        <f>IF(E147="","",E147+F147)</f>
+      </c>
+      <c r="L147" s="11">
+        <f>IF(J147="","",J147-K147)</f>
+      </c>
+      <c r="M147" s="11">
+        <f>IF(G147="","",G147-H147)</f>
+      </c>
+      <c r="N147" s="11">
+        <f>IF(M147="","",M147-I147)</f>
+      </c>
+      <c r="O147" s="11">
+        <f>IF(OR(L147="",L147&lt;=0),"자본잠식",ROUND(K147/L147*100,1))</f>
+      </c>
+      <c r="P147" s="11">
+        <f>IF(OR(L147="",L147&lt;=0),"—",ROUND(N147/L147*100,1))</f>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7"/>
+      <c r="G148" s="7"/>
+      <c r="H148" s="7"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="11">
+        <f>IF(C148="","",C148+D148)</f>
+      </c>
+      <c r="K148" s="11">
+        <f>IF(E148="","",E148+F148)</f>
+      </c>
+      <c r="L148" s="11">
+        <f>IF(J148="","",J148-K148)</f>
+      </c>
+      <c r="M148" s="11">
+        <f>IF(G148="","",G148-H148)</f>
+      </c>
+      <c r="N148" s="11">
+        <f>IF(M148="","",M148-I148)</f>
+      </c>
+      <c r="O148" s="11">
+        <f>IF(OR(L148="",L148&lt;=0),"자본잠식",ROUND(K148/L148*100,1))</f>
+      </c>
+      <c r="P148" s="11">
+        <f>IF(OR(L148="",L148&lt;=0),"—",ROUND(N148/L148*100,1))</f>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
+      <c r="G149" s="7"/>
+      <c r="H149" s="7"/>
+      <c r="I149" s="7"/>
+      <c r="J149" s="11">
+        <f>IF(C149="","",C149+D149)</f>
+      </c>
+      <c r="K149" s="11">
+        <f>IF(E149="","",E149+F149)</f>
+      </c>
+      <c r="L149" s="11">
+        <f>IF(J149="","",J149-K149)</f>
+      </c>
+      <c r="M149" s="11">
+        <f>IF(G149="","",G149-H149)</f>
+      </c>
+      <c r="N149" s="11">
+        <f>IF(M149="","",M149-I149)</f>
+      </c>
+      <c r="O149" s="11">
+        <f>IF(OR(L149="",L149&lt;=0),"자본잠식",ROUND(K149/L149*100,1))</f>
+      </c>
+      <c r="P149" s="11">
+        <f>IF(OR(L149="",L149&lt;=0),"—",ROUND(N149/L149*100,1))</f>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7"/>
+      <c r="B150" s="7"/>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7"/>
+      <c r="G150" s="7"/>
+      <c r="H150" s="7"/>
+      <c r="I150" s="7"/>
+      <c r="J150" s="11">
+        <f>IF(C150="","",C150+D150)</f>
+      </c>
+      <c r="K150" s="11">
+        <f>IF(E150="","",E150+F150)</f>
+      </c>
+      <c r="L150" s="11">
+        <f>IF(J150="","",J150-K150)</f>
+      </c>
+      <c r="M150" s="11">
+        <f>IF(G150="","",G150-H150)</f>
+      </c>
+      <c r="N150" s="11">
+        <f>IF(M150="","",M150-I150)</f>
+      </c>
+      <c r="O150" s="11">
+        <f>IF(OR(L150="",L150&lt;=0),"자본잠식",ROUND(K150/L150*100,1))</f>
+      </c>
+      <c r="P150" s="11">
+        <f>IF(OR(L150="",L150&lt;=0),"—",ROUND(N150/L150*100,1))</f>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7"/>
+      <c r="B151" s="7"/>
+      <c r="C151" s="7"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="7"/>
+      <c r="I151" s="7"/>
+      <c r="J151" s="11">
+        <f>IF(C151="","",C151+D151)</f>
+      </c>
+      <c r="K151" s="11">
+        <f>IF(E151="","",E151+F151)</f>
+      </c>
+      <c r="L151" s="11">
+        <f>IF(J151="","",J151-K151)</f>
+      </c>
+      <c r="M151" s="11">
+        <f>IF(G151="","",G151-H151)</f>
+      </c>
+      <c r="N151" s="11">
+        <f>IF(M151="","",M151-I151)</f>
+      </c>
+      <c r="O151" s="11">
+        <f>IF(OR(L151="",L151&lt;=0),"자본잠식",ROUND(K151/L151*100,1))</f>
+      </c>
+      <c r="P151" s="11">
+        <f>IF(OR(L151="",L151&lt;=0),"—",ROUND(N151/L151*100,1))</f>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7"/>
+      <c r="B152" s="7"/>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="7"/>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
+      <c r="I152" s="7"/>
+      <c r="J152" s="11">
+        <f>IF(C152="","",C152+D152)</f>
+      </c>
+      <c r="K152" s="11">
+        <f>IF(E152="","",E152+F152)</f>
+      </c>
+      <c r="L152" s="11">
+        <f>IF(J152="","",J152-K152)</f>
+      </c>
+      <c r="M152" s="11">
+        <f>IF(G152="","",G152-H152)</f>
+      </c>
+      <c r="N152" s="11">
+        <f>IF(M152="","",M152-I152)</f>
+      </c>
+      <c r="O152" s="11">
+        <f>IF(OR(L152="",L152&lt;=0),"자본잠식",ROUND(K152/L152*100,1))</f>
+      </c>
+      <c r="P152" s="11">
+        <f>IF(OR(L152="",L152&lt;=0),"—",ROUND(N152/L152*100,1))</f>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7"/>
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
+      <c r="I153" s="7"/>
+      <c r="J153" s="11">
+        <f>IF(C153="","",C153+D153)</f>
+      </c>
+      <c r="K153" s="11">
+        <f>IF(E153="","",E153+F153)</f>
+      </c>
+      <c r="L153" s="11">
+        <f>IF(J153="","",J153-K153)</f>
+      </c>
+      <c r="M153" s="11">
+        <f>IF(G153="","",G153-H153)</f>
+      </c>
+      <c r="N153" s="11">
+        <f>IF(M153="","",M153-I153)</f>
+      </c>
+      <c r="O153" s="11">
+        <f>IF(OR(L153="",L153&lt;=0),"자본잠식",ROUND(K153/L153*100,1))</f>
+      </c>
+      <c r="P153" s="11">
+        <f>IF(OR(L153="",L153&lt;=0),"—",ROUND(N153/L153*100,1))</f>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7"/>
+      <c r="B154" s="7"/>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="7"/>
+      <c r="G154" s="7"/>
+      <c r="H154" s="7"/>
+      <c r="I154" s="7"/>
+      <c r="J154" s="11">
+        <f>IF(C154="","",C154+D154)</f>
+      </c>
+      <c r="K154" s="11">
+        <f>IF(E154="","",E154+F154)</f>
+      </c>
+      <c r="L154" s="11">
+        <f>IF(J154="","",J154-K154)</f>
+      </c>
+      <c r="M154" s="11">
+        <f>IF(G154="","",G154-H154)</f>
+      </c>
+      <c r="N154" s="11">
+        <f>IF(M154="","",M154-I154)</f>
+      </c>
+      <c r="O154" s="11">
+        <f>IF(OR(L154="",L154&lt;=0),"자본잠식",ROUND(K154/L154*100,1))</f>
+      </c>
+      <c r="P154" s="11">
+        <f>IF(OR(L154="",L154&lt;=0),"—",ROUND(N154/L154*100,1))</f>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7"/>
+      <c r="B155" s="7"/>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
+      <c r="I155" s="7"/>
+      <c r="J155" s="11">
+        <f>IF(C155="","",C155+D155)</f>
+      </c>
+      <c r="K155" s="11">
+        <f>IF(E155="","",E155+F155)</f>
+      </c>
+      <c r="L155" s="11">
+        <f>IF(J155="","",J155-K155)</f>
+      </c>
+      <c r="M155" s="11">
+        <f>IF(G155="","",G155-H155)</f>
+      </c>
+      <c r="N155" s="11">
+        <f>IF(M155="","",M155-I155)</f>
+      </c>
+      <c r="O155" s="11">
+        <f>IF(OR(L155="",L155&lt;=0),"자본잠식",ROUND(K155/L155*100,1))</f>
+      </c>
+      <c r="P155" s="11">
+        <f>IF(OR(L155="",L155&lt;=0),"—",ROUND(N155/L155*100,1))</f>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7"/>
+      <c r="B156" s="7"/>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+      <c r="I156" s="7"/>
+      <c r="J156" s="11">
+        <f>IF(C156="","",C156+D156)</f>
+      </c>
+      <c r="K156" s="11">
+        <f>IF(E156="","",E156+F156)</f>
+      </c>
+      <c r="L156" s="11">
+        <f>IF(J156="","",J156-K156)</f>
+      </c>
+      <c r="M156" s="11">
+        <f>IF(G156="","",G156-H156)</f>
+      </c>
+      <c r="N156" s="11">
+        <f>IF(M156="","",M156-I156)</f>
+      </c>
+      <c r="O156" s="11">
+        <f>IF(OR(L156="",L156&lt;=0),"자본잠식",ROUND(K156/L156*100,1))</f>
+      </c>
+      <c r="P156" s="11">
+        <f>IF(OR(L156="",L156&lt;=0),"—",ROUND(N156/L156*100,1))</f>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
+      <c r="H157" s="7"/>
+      <c r="I157" s="7"/>
+      <c r="J157" s="11">
+        <f>IF(C157="","",C157+D157)</f>
+      </c>
+      <c r="K157" s="11">
+        <f>IF(E157="","",E157+F157)</f>
+      </c>
+      <c r="L157" s="11">
+        <f>IF(J157="","",J157-K157)</f>
+      </c>
+      <c r="M157" s="11">
+        <f>IF(G157="","",G157-H157)</f>
+      </c>
+      <c r="N157" s="11">
+        <f>IF(M157="","",M157-I157)</f>
+      </c>
+      <c r="O157" s="11">
+        <f>IF(OR(L157="",L157&lt;=0),"자본잠식",ROUND(K157/L157*100,1))</f>
+      </c>
+      <c r="P157" s="11">
+        <f>IF(OR(L157="",L157&lt;=0),"—",ROUND(N157/L157*100,1))</f>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7"/>
+      <c r="B158" s="7"/>
+      <c r="C158" s="7"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="7"/>
+      <c r="G158" s="7"/>
+      <c r="H158" s="7"/>
+      <c r="I158" s="7"/>
+      <c r="J158" s="11">
+        <f>IF(C158="","",C158+D158)</f>
+      </c>
+      <c r="K158" s="11">
+        <f>IF(E158="","",E158+F158)</f>
+      </c>
+      <c r="L158" s="11">
+        <f>IF(J158="","",J158-K158)</f>
+      </c>
+      <c r="M158" s="11">
+        <f>IF(G158="","",G158-H158)</f>
+      </c>
+      <c r="N158" s="11">
+        <f>IF(M158="","",M158-I158)</f>
+      </c>
+      <c r="O158" s="11">
+        <f>IF(OR(L158="",L158&lt;=0),"자본잠식",ROUND(K158/L158*100,1))</f>
+      </c>
+      <c r="P158" s="11">
+        <f>IF(OR(L158="",L158&lt;=0),"—",ROUND(N158/L158*100,1))</f>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7"/>
+      <c r="B159" s="7"/>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="7"/>
+      <c r="I159" s="7"/>
+      <c r="J159" s="11">
+        <f>IF(C159="","",C159+D159)</f>
+      </c>
+      <c r="K159" s="11">
+        <f>IF(E159="","",E159+F159)</f>
+      </c>
+      <c r="L159" s="11">
+        <f>IF(J159="","",J159-K159)</f>
+      </c>
+      <c r="M159" s="11">
+        <f>IF(G159="","",G159-H159)</f>
+      </c>
+      <c r="N159" s="11">
+        <f>IF(M159="","",M159-I159)</f>
+      </c>
+      <c r="O159" s="11">
+        <f>IF(OR(L159="",L159&lt;=0),"자본잠식",ROUND(K159/L159*100,1))</f>
+      </c>
+      <c r="P159" s="11">
+        <f>IF(OR(L159="",L159&lt;=0),"—",ROUND(N159/L159*100,1))</f>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7"/>
+      <c r="B160" s="7"/>
+      <c r="C160" s="7"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="7"/>
+      <c r="H160" s="7"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="11">
+        <f>IF(C160="","",C160+D160)</f>
+      </c>
+      <c r="K160" s="11">
+        <f>IF(E160="","",E160+F160)</f>
+      </c>
+      <c r="L160" s="11">
+        <f>IF(J160="","",J160-K160)</f>
+      </c>
+      <c r="M160" s="11">
+        <f>IF(G160="","",G160-H160)</f>
+      </c>
+      <c r="N160" s="11">
+        <f>IF(M160="","",M160-I160)</f>
+      </c>
+      <c r="O160" s="11">
+        <f>IF(OR(L160="",L160&lt;=0),"자본잠식",ROUND(K160/L160*100,1))</f>
+      </c>
+      <c r="P160" s="11">
+        <f>IF(OR(L160="",L160&lt;=0),"—",ROUND(N160/L160*100,1))</f>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7"/>
+      <c r="B161" s="7"/>
+      <c r="C161" s="7"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="7"/>
+      <c r="G161" s="7"/>
+      <c r="H161" s="7"/>
+      <c r="I161" s="7"/>
+      <c r="J161" s="11">
+        <f>IF(C161="","",C161+D161)</f>
+      </c>
+      <c r="K161" s="11">
+        <f>IF(E161="","",E161+F161)</f>
+      </c>
+      <c r="L161" s="11">
+        <f>IF(J161="","",J161-K161)</f>
+      </c>
+      <c r="M161" s="11">
+        <f>IF(G161="","",G161-H161)</f>
+      </c>
+      <c r="N161" s="11">
+        <f>IF(M161="","",M161-I161)</f>
+      </c>
+      <c r="O161" s="11">
+        <f>IF(OR(L161="",L161&lt;=0),"자본잠식",ROUND(K161/L161*100,1))</f>
+      </c>
+      <c r="P161" s="11">
+        <f>IF(OR(L161="",L161&lt;=0),"—",ROUND(N161/L161*100,1))</f>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7"/>
+      <c r="B162" s="7"/>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="7"/>
+      <c r="G162" s="7"/>
+      <c r="H162" s="7"/>
+      <c r="I162" s="7"/>
+      <c r="J162" s="11">
+        <f>IF(C162="","",C162+D162)</f>
+      </c>
+      <c r="K162" s="11">
+        <f>IF(E162="","",E162+F162)</f>
+      </c>
+      <c r="L162" s="11">
+        <f>IF(J162="","",J162-K162)</f>
+      </c>
+      <c r="M162" s="11">
+        <f>IF(G162="","",G162-H162)</f>
+      </c>
+      <c r="N162" s="11">
+        <f>IF(M162="","",M162-I162)</f>
+      </c>
+      <c r="O162" s="11">
+        <f>IF(OR(L162="",L162&lt;=0),"자본잠식",ROUND(K162/L162*100,1))</f>
+      </c>
+      <c r="P162" s="11">
+        <f>IF(OR(L162="",L162&lt;=0),"—",ROUND(N162/L162*100,1))</f>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7"/>
+      <c r="B163" s="7"/>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="7"/>
+      <c r="H163" s="7"/>
+      <c r="I163" s="7"/>
+      <c r="J163" s="11">
+        <f>IF(C163="","",C163+D163)</f>
+      </c>
+      <c r="K163" s="11">
+        <f>IF(E163="","",E163+F163)</f>
+      </c>
+      <c r="L163" s="11">
+        <f>IF(J163="","",J163-K163)</f>
+      </c>
+      <c r="M163" s="11">
+        <f>IF(G163="","",G163-H163)</f>
+      </c>
+      <c r="N163" s="11">
+        <f>IF(M163="","",M163-I163)</f>
+      </c>
+      <c r="O163" s="11">
+        <f>IF(OR(L163="",L163&lt;=0),"자본잠식",ROUND(K163/L163*100,1))</f>
+      </c>
+      <c r="P163" s="11">
+        <f>IF(OR(L163="",L163&lt;=0),"—",ROUND(N163/L163*100,1))</f>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7"/>
+      <c r="B164" s="7"/>
+      <c r="C164" s="7"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="7"/>
+      <c r="H164" s="7"/>
+      <c r="I164" s="7"/>
+      <c r="J164" s="11">
+        <f>IF(C164="","",C164+D164)</f>
+      </c>
+      <c r="K164" s="11">
+        <f>IF(E164="","",E164+F164)</f>
+      </c>
+      <c r="L164" s="11">
+        <f>IF(J164="","",J164-K164)</f>
+      </c>
+      <c r="M164" s="11">
+        <f>IF(G164="","",G164-H164)</f>
+      </c>
+      <c r="N164" s="11">
+        <f>IF(M164="","",M164-I164)</f>
+      </c>
+      <c r="O164" s="11">
+        <f>IF(OR(L164="",L164&lt;=0),"자본잠식",ROUND(K164/L164*100,1))</f>
+      </c>
+      <c r="P164" s="11">
+        <f>IF(OR(L164="",L164&lt;=0),"—",ROUND(N164/L164*100,1))</f>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="7"/>
+      <c r="H165" s="7"/>
+      <c r="I165" s="7"/>
+      <c r="J165" s="11">
+        <f>IF(C165="","",C165+D165)</f>
+      </c>
+      <c r="K165" s="11">
+        <f>IF(E165="","",E165+F165)</f>
+      </c>
+      <c r="L165" s="11">
+        <f>IF(J165="","",J165-K165)</f>
+      </c>
+      <c r="M165" s="11">
+        <f>IF(G165="","",G165-H165)</f>
+      </c>
+      <c r="N165" s="11">
+        <f>IF(M165="","",M165-I165)</f>
+      </c>
+      <c r="O165" s="11">
+        <f>IF(OR(L165="",L165&lt;=0),"자본잠식",ROUND(K165/L165*100,1))</f>
+      </c>
+      <c r="P165" s="11">
+        <f>IF(OR(L165="",L165&lt;=0),"—",ROUND(N165/L165*100,1))</f>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7"/>
+      <c r="B166" s="7"/>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="7"/>
+      <c r="H166" s="7"/>
+      <c r="I166" s="7"/>
+      <c r="J166" s="11">
+        <f>IF(C166="","",C166+D166)</f>
+      </c>
+      <c r="K166" s="11">
+        <f>IF(E166="","",E166+F166)</f>
+      </c>
+      <c r="L166" s="11">
+        <f>IF(J166="","",J166-K166)</f>
+      </c>
+      <c r="M166" s="11">
+        <f>IF(G166="","",G166-H166)</f>
+      </c>
+      <c r="N166" s="11">
+        <f>IF(M166="","",M166-I166)</f>
+      </c>
+      <c r="O166" s="11">
+        <f>IF(OR(L166="",L166&lt;=0),"자본잠식",ROUND(K166/L166*100,1))</f>
+      </c>
+      <c r="P166" s="11">
+        <f>IF(OR(L166="",L166&lt;=0),"—",ROUND(N166/L166*100,1))</f>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7"/>
+      <c r="B167" s="7"/>
+      <c r="C167" s="7"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
+      <c r="G167" s="7"/>
+      <c r="H167" s="7"/>
+      <c r="I167" s="7"/>
+      <c r="J167" s="11">
+        <f>IF(C167="","",C167+D167)</f>
+      </c>
+      <c r="K167" s="11">
+        <f>IF(E167="","",E167+F167)</f>
+      </c>
+      <c r="L167" s="11">
+        <f>IF(J167="","",J167-K167)</f>
+      </c>
+      <c r="M167" s="11">
+        <f>IF(G167="","",G167-H167)</f>
+      </c>
+      <c r="N167" s="11">
+        <f>IF(M167="","",M167-I167)</f>
+      </c>
+      <c r="O167" s="11">
+        <f>IF(OR(L167="",L167&lt;=0),"자본잠식",ROUND(K167/L167*100,1))</f>
+      </c>
+      <c r="P167" s="11">
+        <f>IF(OR(L167="",L167&lt;=0),"—",ROUND(N167/L167*100,1))</f>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7"/>
+      <c r="B168" s="7"/>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+      <c r="G168" s="7"/>
+      <c r="H168" s="7"/>
+      <c r="I168" s="7"/>
+      <c r="J168" s="11">
+        <f>IF(C168="","",C168+D168)</f>
+      </c>
+      <c r="K168" s="11">
+        <f>IF(E168="","",E168+F168)</f>
+      </c>
+      <c r="L168" s="11">
+        <f>IF(J168="","",J168-K168)</f>
+      </c>
+      <c r="M168" s="11">
+        <f>IF(G168="","",G168-H168)</f>
+      </c>
+      <c r="N168" s="11">
+        <f>IF(M168="","",M168-I168)</f>
+      </c>
+      <c r="O168" s="11">
+        <f>IF(OR(L168="",L168&lt;=0),"자본잠식",ROUND(K168/L168*100,1))</f>
+      </c>
+      <c r="P168" s="11">
+        <f>IF(OR(L168="",L168&lt;=0),"—",ROUND(N168/L168*100,1))</f>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="7"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
+      <c r="G169" s="7"/>
+      <c r="H169" s="7"/>
+      <c r="I169" s="7"/>
+      <c r="J169" s="11">
+        <f>IF(C169="","",C169+D169)</f>
+      </c>
+      <c r="K169" s="11">
+        <f>IF(E169="","",E169+F169)</f>
+      </c>
+      <c r="L169" s="11">
+        <f>IF(J169="","",J169-K169)</f>
+      </c>
+      <c r="M169" s="11">
+        <f>IF(G169="","",G169-H169)</f>
+      </c>
+      <c r="N169" s="11">
+        <f>IF(M169="","",M169-I169)</f>
+      </c>
+      <c r="O169" s="11">
+        <f>IF(OR(L169="",L169&lt;=0),"자본잠식",ROUND(K169/L169*100,1))</f>
+      </c>
+      <c r="P169" s="11">
+        <f>IF(OR(L169="",L169&lt;=0),"—",ROUND(N169/L169*100,1))</f>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7"/>
+      <c r="B170" s="7"/>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7"/>
+      <c r="G170" s="7"/>
+      <c r="H170" s="7"/>
+      <c r="I170" s="7"/>
+      <c r="J170" s="11">
+        <f>IF(C170="","",C170+D170)</f>
+      </c>
+      <c r="K170" s="11">
+        <f>IF(E170="","",E170+F170)</f>
+      </c>
+      <c r="L170" s="11">
+        <f>IF(J170="","",J170-K170)</f>
+      </c>
+      <c r="M170" s="11">
+        <f>IF(G170="","",G170-H170)</f>
+      </c>
+      <c r="N170" s="11">
+        <f>IF(M170="","",M170-I170)</f>
+      </c>
+      <c r="O170" s="11">
+        <f>IF(OR(L170="",L170&lt;=0),"자본잠식",ROUND(K170/L170*100,1))</f>
+      </c>
+      <c r="P170" s="11">
+        <f>IF(OR(L170="",L170&lt;=0),"—",ROUND(N170/L170*100,1))</f>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7"/>
+      <c r="B171" s="7"/>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
+      <c r="G171" s="7"/>
+      <c r="H171" s="7"/>
+      <c r="I171" s="7"/>
+      <c r="J171" s="11">
+        <f>IF(C171="","",C171+D171)</f>
+      </c>
+      <c r="K171" s="11">
+        <f>IF(E171="","",E171+F171)</f>
+      </c>
+      <c r="L171" s="11">
+        <f>IF(J171="","",J171-K171)</f>
+      </c>
+      <c r="M171" s="11">
+        <f>IF(G171="","",G171-H171)</f>
+      </c>
+      <c r="N171" s="11">
+        <f>IF(M171="","",M171-I171)</f>
+      </c>
+      <c r="O171" s="11">
+        <f>IF(OR(L171="",L171&lt;=0),"자본잠식",ROUND(K171/L171*100,1))</f>
+      </c>
+      <c r="P171" s="11">
+        <f>IF(OR(L171="",L171&lt;=0),"—",ROUND(N171/L171*100,1))</f>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="7"/>
+      <c r="B172" s="7"/>
+      <c r="C172" s="7"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
+      <c r="F172" s="7"/>
+      <c r="G172" s="7"/>
+      <c r="H172" s="7"/>
+      <c r="I172" s="7"/>
+      <c r="J172" s="11">
+        <f>IF(C172="","",C172+D172)</f>
+      </c>
+      <c r="K172" s="11">
+        <f>IF(E172="","",E172+F172)</f>
+      </c>
+      <c r="L172" s="11">
+        <f>IF(J172="","",J172-K172)</f>
+      </c>
+      <c r="M172" s="11">
+        <f>IF(G172="","",G172-H172)</f>
+      </c>
+      <c r="N172" s="11">
+        <f>IF(M172="","",M172-I172)</f>
+      </c>
+      <c r="O172" s="11">
+        <f>IF(OR(L172="",L172&lt;=0),"자본잠식",ROUND(K172/L172*100,1))</f>
+      </c>
+      <c r="P172" s="11">
+        <f>IF(OR(L172="",L172&lt;=0),"—",ROUND(N172/L172*100,1))</f>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="7"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7"/>
+      <c r="G173" s="7"/>
+      <c r="H173" s="7"/>
+      <c r="I173" s="7"/>
+      <c r="J173" s="11">
+        <f>IF(C173="","",C173+D173)</f>
+      </c>
+      <c r="K173" s="11">
+        <f>IF(E173="","",E173+F173)</f>
+      </c>
+      <c r="L173" s="11">
+        <f>IF(J173="","",J173-K173)</f>
+      </c>
+      <c r="M173" s="11">
+        <f>IF(G173="","",G173-H173)</f>
+      </c>
+      <c r="N173" s="11">
+        <f>IF(M173="","",M173-I173)</f>
+      </c>
+      <c r="O173" s="11">
+        <f>IF(OR(L173="",L173&lt;=0),"자본잠식",ROUND(K173/L173*100,1))</f>
+      </c>
+      <c r="P173" s="11">
+        <f>IF(OR(L173="",L173&lt;=0),"—",ROUND(N173/L173*100,1))</f>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7"/>
+      <c r="B174" s="7"/>
+      <c r="C174" s="7"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
+      <c r="F174" s="7"/>
+      <c r="G174" s="7"/>
+      <c r="H174" s="7"/>
+      <c r="I174" s="7"/>
+      <c r="J174" s="11">
+        <f>IF(C174="","",C174+D174)</f>
+      </c>
+      <c r="K174" s="11">
+        <f>IF(E174="","",E174+F174)</f>
+      </c>
+      <c r="L174" s="11">
+        <f>IF(J174="","",J174-K174)</f>
+      </c>
+      <c r="M174" s="11">
+        <f>IF(G174="","",G174-H174)</f>
+      </c>
+      <c r="N174" s="11">
+        <f>IF(M174="","",M174-I174)</f>
+      </c>
+      <c r="O174" s="11">
+        <f>IF(OR(L174="",L174&lt;=0),"자본잠식",ROUND(K174/L174*100,1))</f>
+      </c>
+      <c r="P174" s="11">
+        <f>IF(OR(L174="",L174&lt;=0),"—",ROUND(N174/L174*100,1))</f>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="7"/>
+      <c r="B175" s="7"/>
+      <c r="C175" s="7"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7"/>
+      <c r="G175" s="7"/>
+      <c r="H175" s="7"/>
+      <c r="I175" s="7"/>
+      <c r="J175" s="11">
+        <f>IF(C175="","",C175+D175)</f>
+      </c>
+      <c r="K175" s="11">
+        <f>IF(E175="","",E175+F175)</f>
+      </c>
+      <c r="L175" s="11">
+        <f>IF(J175="","",J175-K175)</f>
+      </c>
+      <c r="M175" s="11">
+        <f>IF(G175="","",G175-H175)</f>
+      </c>
+      <c r="N175" s="11">
+        <f>IF(M175="","",M175-I175)</f>
+      </c>
+      <c r="O175" s="11">
+        <f>IF(OR(L175="",L175&lt;=0),"자본잠식",ROUND(K175/L175*100,1))</f>
+      </c>
+      <c r="P175" s="11">
+        <f>IF(OR(L175="",L175&lt;=0),"—",ROUND(N175/L175*100,1))</f>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="7"/>
+      <c r="B176" s="7"/>
+      <c r="C176" s="7"/>
+      <c r="D176" s="7"/>
+      <c r="E176" s="7"/>
+      <c r="F176" s="7"/>
+      <c r="G176" s="7"/>
+      <c r="H176" s="7"/>
+      <c r="I176" s="7"/>
+      <c r="J176" s="11">
+        <f>IF(C176="","",C176+D176)</f>
+      </c>
+      <c r="K176" s="11">
+        <f>IF(E176="","",E176+F176)</f>
+      </c>
+      <c r="L176" s="11">
+        <f>IF(J176="","",J176-K176)</f>
+      </c>
+      <c r="M176" s="11">
+        <f>IF(G176="","",G176-H176)</f>
+      </c>
+      <c r="N176" s="11">
+        <f>IF(M176="","",M176-I176)</f>
+      </c>
+      <c r="O176" s="11">
+        <f>IF(OR(L176="",L176&lt;=0),"자본잠식",ROUND(K176/L176*100,1))</f>
+      </c>
+      <c r="P176" s="11">
+        <f>IF(OR(L176="",L176&lt;=0),"—",ROUND(N176/L176*100,1))</f>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7"/>
+      <c r="B177" s="7"/>
+      <c r="C177" s="7"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
+      <c r="G177" s="7"/>
+      <c r="H177" s="7"/>
+      <c r="I177" s="7"/>
+      <c r="J177" s="11">
+        <f>IF(C177="","",C177+D177)</f>
+      </c>
+      <c r="K177" s="11">
+        <f>IF(E177="","",E177+F177)</f>
+      </c>
+      <c r="L177" s="11">
+        <f>IF(J177="","",J177-K177)</f>
+      </c>
+      <c r="M177" s="11">
+        <f>IF(G177="","",G177-H177)</f>
+      </c>
+      <c r="N177" s="11">
+        <f>IF(M177="","",M177-I177)</f>
+      </c>
+      <c r="O177" s="11">
+        <f>IF(OR(L177="",L177&lt;=0),"자본잠식",ROUND(K177/L177*100,1))</f>
+      </c>
+      <c r="P177" s="11">
+        <f>IF(OR(L177="",L177&lt;=0),"—",ROUND(N177/L177*100,1))</f>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="7"/>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="7"/>
+      <c r="H178" s="7"/>
+      <c r="I178" s="7"/>
+      <c r="J178" s="11">
+        <f>IF(C178="","",C178+D178)</f>
+      </c>
+      <c r="K178" s="11">
+        <f>IF(E178="","",E178+F178)</f>
+      </c>
+      <c r="L178" s="11">
+        <f>IF(J178="","",J178-K178)</f>
+      </c>
+      <c r="M178" s="11">
+        <f>IF(G178="","",G178-H178)</f>
+      </c>
+      <c r="N178" s="11">
+        <f>IF(M178="","",M178-I178)</f>
+      </c>
+      <c r="O178" s="11">
+        <f>IF(OR(L178="",L178&lt;=0),"자본잠식",ROUND(K178/L178*100,1))</f>
+      </c>
+      <c r="P178" s="11">
+        <f>IF(OR(L178="",L178&lt;=0),"—",ROUND(N178/L178*100,1))</f>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="7"/>
+      <c r="B179" s="7"/>
+      <c r="C179" s="7"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="7"/>
+      <c r="F179" s="7"/>
+      <c r="G179" s="7"/>
+      <c r="H179" s="7"/>
+      <c r="I179" s="7"/>
+      <c r="J179" s="11">
+        <f>IF(C179="","",C179+D179)</f>
+      </c>
+      <c r="K179" s="11">
+        <f>IF(E179="","",E179+F179)</f>
+      </c>
+      <c r="L179" s="11">
+        <f>IF(J179="","",J179-K179)</f>
+      </c>
+      <c r="M179" s="11">
+        <f>IF(G179="","",G179-H179)</f>
+      </c>
+      <c r="N179" s="11">
+        <f>IF(M179="","",M179-I179)</f>
+      </c>
+      <c r="O179" s="11">
+        <f>IF(OR(L179="",L179&lt;=0),"자본잠식",ROUND(K179/L179*100,1))</f>
+      </c>
+      <c r="P179" s="11">
+        <f>IF(OR(L179="",L179&lt;=0),"—",ROUND(N179/L179*100,1))</f>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="7"/>
+      <c r="B180" s="7"/>
+      <c r="C180" s="7"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="7"/>
+      <c r="F180" s="7"/>
+      <c r="G180" s="7"/>
+      <c r="H180" s="7"/>
+      <c r="I180" s="7"/>
+      <c r="J180" s="11">
+        <f>IF(C180="","",C180+D180)</f>
+      </c>
+      <c r="K180" s="11">
+        <f>IF(E180="","",E180+F180)</f>
+      </c>
+      <c r="L180" s="11">
+        <f>IF(J180="","",J180-K180)</f>
+      </c>
+      <c r="M180" s="11">
+        <f>IF(G180="","",G180-H180)</f>
+      </c>
+      <c r="N180" s="11">
+        <f>IF(M180="","",M180-I180)</f>
+      </c>
+      <c r="O180" s="11">
+        <f>IF(OR(L180="",L180&lt;=0),"자본잠식",ROUND(K180/L180*100,1))</f>
+      </c>
+      <c r="P180" s="11">
+        <f>IF(OR(L180="",L180&lt;=0),"—",ROUND(N180/L180*100,1))</f>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7"/>
+      <c r="B181" s="7"/>
+      <c r="C181" s="7"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="7"/>
+      <c r="F181" s="7"/>
+      <c r="G181" s="7"/>
+      <c r="H181" s="7"/>
+      <c r="I181" s="7"/>
+      <c r="J181" s="11">
+        <f>IF(C181="","",C181+D181)</f>
+      </c>
+      <c r="K181" s="11">
+        <f>IF(E181="","",E181+F181)</f>
+      </c>
+      <c r="L181" s="11">
+        <f>IF(J181="","",J181-K181)</f>
+      </c>
+      <c r="M181" s="11">
+        <f>IF(G181="","",G181-H181)</f>
+      </c>
+      <c r="N181" s="11">
+        <f>IF(M181="","",M181-I181)</f>
+      </c>
+      <c r="O181" s="11">
+        <f>IF(OR(L181="",L181&lt;=0),"자본잠식",ROUND(K181/L181*100,1))</f>
+      </c>
+      <c r="P181" s="11">
+        <f>IF(OR(L181="",L181&lt;=0),"—",ROUND(N181/L181*100,1))</f>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="7"/>
+      <c r="B182" s="7"/>
+      <c r="C182" s="7"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7"/>
+      <c r="G182" s="7"/>
+      <c r="H182" s="7"/>
+      <c r="I182" s="7"/>
+      <c r="J182" s="11">
+        <f>IF(C182="","",C182+D182)</f>
+      </c>
+      <c r="K182" s="11">
+        <f>IF(E182="","",E182+F182)</f>
+      </c>
+      <c r="L182" s="11">
+        <f>IF(J182="","",J182-K182)</f>
+      </c>
+      <c r="M182" s="11">
+        <f>IF(G182="","",G182-H182)</f>
+      </c>
+      <c r="N182" s="11">
+        <f>IF(M182="","",M182-I182)</f>
+      </c>
+      <c r="O182" s="11">
+        <f>IF(OR(L182="",L182&lt;=0),"자본잠식",ROUND(K182/L182*100,1))</f>
+      </c>
+      <c r="P182" s="11">
+        <f>IF(OR(L182="",L182&lt;=0),"—",ROUND(N182/L182*100,1))</f>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="7"/>
+      <c r="B183" s="7"/>
+      <c r="C183" s="7"/>
+      <c r="D183" s="7"/>
+      <c r="E183" s="7"/>
+      <c r="F183" s="7"/>
+      <c r="G183" s="7"/>
+      <c r="H183" s="7"/>
+      <c r="I183" s="7"/>
+      <c r="J183" s="11">
+        <f>IF(C183="","",C183+D183)</f>
+      </c>
+      <c r="K183" s="11">
+        <f>IF(E183="","",E183+F183)</f>
+      </c>
+      <c r="L183" s="11">
+        <f>IF(J183="","",J183-K183)</f>
+      </c>
+      <c r="M183" s="11">
+        <f>IF(G183="","",G183-H183)</f>
+      </c>
+      <c r="N183" s="11">
+        <f>IF(M183="","",M183-I183)</f>
+      </c>
+      <c r="O183" s="11">
+        <f>IF(OR(L183="",L183&lt;=0),"자본잠식",ROUND(K183/L183*100,1))</f>
+      </c>
+      <c r="P183" s="11">
+        <f>IF(OR(L183="",L183&lt;=0),"—",ROUND(N183/L183*100,1))</f>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="7"/>
+      <c r="B184" s="7"/>
+      <c r="C184" s="7"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="7"/>
+      <c r="F184" s="7"/>
+      <c r="G184" s="7"/>
+      <c r="H184" s="7"/>
+      <c r="I184" s="7"/>
+      <c r="J184" s="11">
+        <f>IF(C184="","",C184+D184)</f>
+      </c>
+      <c r="K184" s="11">
+        <f>IF(E184="","",E184+F184)</f>
+      </c>
+      <c r="L184" s="11">
+        <f>IF(J184="","",J184-K184)</f>
+      </c>
+      <c r="M184" s="11">
+        <f>IF(G184="","",G184-H184)</f>
+      </c>
+      <c r="N184" s="11">
+        <f>IF(M184="","",M184-I184)</f>
+      </c>
+      <c r="O184" s="11">
+        <f>IF(OR(L184="",L184&lt;=0),"자본잠식",ROUND(K184/L184*100,1))</f>
+      </c>
+      <c r="P184" s="11">
+        <f>IF(OR(L184="",L184&lt;=0),"—",ROUND(N184/L184*100,1))</f>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="7"/>
+      <c r="B185" s="7"/>
+      <c r="C185" s="7"/>
+      <c r="D185" s="7"/>
+      <c r="E185" s="7"/>
+      <c r="F185" s="7"/>
+      <c r="G185" s="7"/>
+      <c r="H185" s="7"/>
+      <c r="I185" s="7"/>
+      <c r="J185" s="11">
+        <f>IF(C185="","",C185+D185)</f>
+      </c>
+      <c r="K185" s="11">
+        <f>IF(E185="","",E185+F185)</f>
+      </c>
+      <c r="L185" s="11">
+        <f>IF(J185="","",J185-K185)</f>
+      </c>
+      <c r="M185" s="11">
+        <f>IF(G185="","",G185-H185)</f>
+      </c>
+      <c r="N185" s="11">
+        <f>IF(M185="","",M185-I185)</f>
+      </c>
+      <c r="O185" s="11">
+        <f>IF(OR(L185="",L185&lt;=0),"자본잠식",ROUND(K185/L185*100,1))</f>
+      </c>
+      <c r="P185" s="11">
+        <f>IF(OR(L185="",L185&lt;=0),"—",ROUND(N185/L185*100,1))</f>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7"/>
+      <c r="B186" s="7"/>
+      <c r="C186" s="7"/>
+      <c r="D186" s="7"/>
+      <c r="E186" s="7"/>
+      <c r="F186" s="7"/>
+      <c r="G186" s="7"/>
+      <c r="H186" s="7"/>
+      <c r="I186" s="7"/>
+      <c r="J186" s="11">
+        <f>IF(C186="","",C186+D186)</f>
+      </c>
+      <c r="K186" s="11">
+        <f>IF(E186="","",E186+F186)</f>
+      </c>
+      <c r="L186" s="11">
+        <f>IF(J186="","",J186-K186)</f>
+      </c>
+      <c r="M186" s="11">
+        <f>IF(G186="","",G186-H186)</f>
+      </c>
+      <c r="N186" s="11">
+        <f>IF(M186="","",M186-I186)</f>
+      </c>
+      <c r="O186" s="11">
+        <f>IF(OR(L186="",L186&lt;=0),"자본잠식",ROUND(K186/L186*100,1))</f>
+      </c>
+      <c r="P186" s="11">
+        <f>IF(OR(L186="",L186&lt;=0),"—",ROUND(N186/L186*100,1))</f>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="7"/>
+      <c r="B187" s="7"/>
+      <c r="C187" s="7"/>
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7"/>
+      <c r="G187" s="7"/>
+      <c r="H187" s="7"/>
+      <c r="I187" s="7"/>
+      <c r="J187" s="11">
+        <f>IF(C187="","",C187+D187)</f>
+      </c>
+      <c r="K187" s="11">
+        <f>IF(E187="","",E187+F187)</f>
+      </c>
+      <c r="L187" s="11">
+        <f>IF(J187="","",J187-K187)</f>
+      </c>
+      <c r="M187" s="11">
+        <f>IF(G187="","",G187-H187)</f>
+      </c>
+      <c r="N187" s="11">
+        <f>IF(M187="","",M187-I187)</f>
+      </c>
+      <c r="O187" s="11">
+        <f>IF(OR(L187="",L187&lt;=0),"자본잠식",ROUND(K187/L187*100,1))</f>
+      </c>
+      <c r="P187" s="11">
+        <f>IF(OR(L187="",L187&lt;=0),"—",ROUND(N187/L187*100,1))</f>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="7"/>
+      <c r="B188" s="7"/>
+      <c r="C188" s="7"/>
+      <c r="D188" s="7"/>
+      <c r="E188" s="7"/>
+      <c r="F188" s="7"/>
+      <c r="G188" s="7"/>
+      <c r="H188" s="7"/>
+      <c r="I188" s="7"/>
+      <c r="J188" s="11">
+        <f>IF(C188="","",C188+D188)</f>
+      </c>
+      <c r="K188" s="11">
+        <f>IF(E188="","",E188+F188)</f>
+      </c>
+      <c r="L188" s="11">
+        <f>IF(J188="","",J188-K188)</f>
+      </c>
+      <c r="M188" s="11">
+        <f>IF(G188="","",G188-H188)</f>
+      </c>
+      <c r="N188" s="11">
+        <f>IF(M188="","",M188-I188)</f>
+      </c>
+      <c r="O188" s="11">
+        <f>IF(OR(L188="",L188&lt;=0),"자본잠식",ROUND(K188/L188*100,1))</f>
+      </c>
+      <c r="P188" s="11">
+        <f>IF(OR(L188="",L188&lt;=0),"—",ROUND(N188/L188*100,1))</f>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="7"/>
+      <c r="B189" s="7"/>
+      <c r="C189" s="7"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
+      <c r="G189" s="7"/>
+      <c r="H189" s="7"/>
+      <c r="I189" s="7"/>
+      <c r="J189" s="11">
+        <f>IF(C189="","",C189+D189)</f>
+      </c>
+      <c r="K189" s="11">
+        <f>IF(E189="","",E189+F189)</f>
+      </c>
+      <c r="L189" s="11">
+        <f>IF(J189="","",J189-K189)</f>
+      </c>
+      <c r="M189" s="11">
+        <f>IF(G189="","",G189-H189)</f>
+      </c>
+      <c r="N189" s="11">
+        <f>IF(M189="","",M189-I189)</f>
+      </c>
+      <c r="O189" s="11">
+        <f>IF(OR(L189="",L189&lt;=0),"자본잠식",ROUND(K189/L189*100,1))</f>
+      </c>
+      <c r="P189" s="11">
+        <f>IF(OR(L189="",L189&lt;=0),"—",ROUND(N189/L189*100,1))</f>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="7"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="7"/>
+      <c r="D190" s="7"/>
+      <c r="E190" s="7"/>
+      <c r="F190" s="7"/>
+      <c r="G190" s="7"/>
+      <c r="H190" s="7"/>
+      <c r="I190" s="7"/>
+      <c r="J190" s="11">
+        <f>IF(C190="","",C190+D190)</f>
+      </c>
+      <c r="K190" s="11">
+        <f>IF(E190="","",E190+F190)</f>
+      </c>
+      <c r="L190" s="11">
+        <f>IF(J190="","",J190-K190)</f>
+      </c>
+      <c r="M190" s="11">
+        <f>IF(G190="","",G190-H190)</f>
+      </c>
+      <c r="N190" s="11">
+        <f>IF(M190="","",M190-I190)</f>
+      </c>
+      <c r="O190" s="11">
+        <f>IF(OR(L190="",L190&lt;=0),"자본잠식",ROUND(K190/L190*100,1))</f>
+      </c>
+      <c r="P190" s="11">
+        <f>IF(OR(L190="",L190&lt;=0),"—",ROUND(N190/L190*100,1))</f>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="7"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="7"/>
+      <c r="D191" s="7"/>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7"/>
+      <c r="G191" s="7"/>
+      <c r="H191" s="7"/>
+      <c r="I191" s="7"/>
+      <c r="J191" s="11">
+        <f>IF(C191="","",C191+D191)</f>
+      </c>
+      <c r="K191" s="11">
+        <f>IF(E191="","",E191+F191)</f>
+      </c>
+      <c r="L191" s="11">
+        <f>IF(J191="","",J191-K191)</f>
+      </c>
+      <c r="M191" s="11">
+        <f>IF(G191="","",G191-H191)</f>
+      </c>
+      <c r="N191" s="11">
+        <f>IF(M191="","",M191-I191)</f>
+      </c>
+      <c r="O191" s="11">
+        <f>IF(OR(L191="",L191&lt;=0),"자본잠식",ROUND(K191/L191*100,1))</f>
+      </c>
+      <c r="P191" s="11">
+        <f>IF(OR(L191="",L191&lt;=0),"—",ROUND(N191/L191*100,1))</f>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="7"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="7"/>
+      <c r="D192" s="7"/>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7"/>
+      <c r="G192" s="7"/>
+      <c r="H192" s="7"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="11">
+        <f>IF(C192="","",C192+D192)</f>
+      </c>
+      <c r="K192" s="11">
+        <f>IF(E192="","",E192+F192)</f>
+      </c>
+      <c r="L192" s="11">
+        <f>IF(J192="","",J192-K192)</f>
+      </c>
+      <c r="M192" s="11">
+        <f>IF(G192="","",G192-H192)</f>
+      </c>
+      <c r="N192" s="11">
+        <f>IF(M192="","",M192-I192)</f>
+      </c>
+      <c r="O192" s="11">
+        <f>IF(OR(L192="",L192&lt;=0),"자본잠식",ROUND(K192/L192*100,1))</f>
+      </c>
+      <c r="P192" s="11">
+        <f>IF(OR(L192="",L192&lt;=0),"—",ROUND(N192/L192*100,1))</f>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="7"/>
+      <c r="B193" s="7"/>
+      <c r="C193" s="7"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7"/>
+      <c r="F193" s="7"/>
+      <c r="G193" s="7"/>
+      <c r="H193" s="7"/>
+      <c r="I193" s="7"/>
+      <c r="J193" s="11">
+        <f>IF(C193="","",C193+D193)</f>
+      </c>
+      <c r="K193" s="11">
+        <f>IF(E193="","",E193+F193)</f>
+      </c>
+      <c r="L193" s="11">
+        <f>IF(J193="","",J193-K193)</f>
+      </c>
+      <c r="M193" s="11">
+        <f>IF(G193="","",G193-H193)</f>
+      </c>
+      <c r="N193" s="11">
+        <f>IF(M193="","",M193-I193)</f>
+      </c>
+      <c r="O193" s="11">
+        <f>IF(OR(L193="",L193&lt;=0),"자본잠식",ROUND(K193/L193*100,1))</f>
+      </c>
+      <c r="P193" s="11">
+        <f>IF(OR(L193="",L193&lt;=0),"—",ROUND(N193/L193*100,1))</f>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="7"/>
+      <c r="B194" s="7"/>
+      <c r="C194" s="7"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7"/>
+      <c r="G194" s="7"/>
+      <c r="H194" s="7"/>
+      <c r="I194" s="7"/>
+      <c r="J194" s="11">
+        <f>IF(C194="","",C194+D194)</f>
+      </c>
+      <c r="K194" s="11">
+        <f>IF(E194="","",E194+F194)</f>
+      </c>
+      <c r="L194" s="11">
+        <f>IF(J194="","",J194-K194)</f>
+      </c>
+      <c r="M194" s="11">
+        <f>IF(G194="","",G194-H194)</f>
+      </c>
+      <c r="N194" s="11">
+        <f>IF(M194="","",M194-I194)</f>
+      </c>
+      <c r="O194" s="11">
+        <f>IF(OR(L194="",L194&lt;=0),"자본잠식",ROUND(K194/L194*100,1))</f>
+      </c>
+      <c r="P194" s="11">
+        <f>IF(OR(L194="",L194&lt;=0),"—",ROUND(N194/L194*100,1))</f>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="7"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="7"/>
+      <c r="D195" s="7"/>
+      <c r="E195" s="7"/>
+      <c r="F195" s="7"/>
+      <c r="G195" s="7"/>
+      <c r="H195" s="7"/>
+      <c r="I195" s="7"/>
+      <c r="J195" s="11">
+        <f>IF(C195="","",C195+D195)</f>
+      </c>
+      <c r="K195" s="11">
+        <f>IF(E195="","",E195+F195)</f>
+      </c>
+      <c r="L195" s="11">
+        <f>IF(J195="","",J195-K195)</f>
+      </c>
+      <c r="M195" s="11">
+        <f>IF(G195="","",G195-H195)</f>
+      </c>
+      <c r="N195" s="11">
+        <f>IF(M195="","",M195-I195)</f>
+      </c>
+      <c r="O195" s="11">
+        <f>IF(OR(L195="",L195&lt;=0),"자본잠식",ROUND(K195/L195*100,1))</f>
+      </c>
+      <c r="P195" s="11">
+        <f>IF(OR(L195="",L195&lt;=0),"—",ROUND(N195/L195*100,1))</f>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="7"/>
+      <c r="B196" s="7"/>
+      <c r="C196" s="7"/>
+      <c r="D196" s="7"/>
+      <c r="E196" s="7"/>
+      <c r="F196" s="7"/>
+      <c r="G196" s="7"/>
+      <c r="H196" s="7"/>
+      <c r="I196" s="7"/>
+      <c r="J196" s="11">
+        <f>IF(C196="","",C196+D196)</f>
+      </c>
+      <c r="K196" s="11">
+        <f>IF(E196="","",E196+F196)</f>
+      </c>
+      <c r="L196" s="11">
+        <f>IF(J196="","",J196-K196)</f>
+      </c>
+      <c r="M196" s="11">
+        <f>IF(G196="","",G196-H196)</f>
+      </c>
+      <c r="N196" s="11">
+        <f>IF(M196="","",M196-I196)</f>
+      </c>
+      <c r="O196" s="11">
+        <f>IF(OR(L196="",L196&lt;=0),"자본잠식",ROUND(K196/L196*100,1))</f>
+      </c>
+      <c r="P196" s="11">
+        <f>IF(OR(L196="",L196&lt;=0),"—",ROUND(N196/L196*100,1))</f>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7"/>
+      <c r="B197" s="7"/>
+      <c r="C197" s="7"/>
+      <c r="D197" s="7"/>
+      <c r="E197" s="7"/>
+      <c r="F197" s="7"/>
+      <c r="G197" s="7"/>
+      <c r="H197" s="7"/>
+      <c r="I197" s="7"/>
+      <c r="J197" s="11">
+        <f>IF(C197="","",C197+D197)</f>
+      </c>
+      <c r="K197" s="11">
+        <f>IF(E197="","",E197+F197)</f>
+      </c>
+      <c r="L197" s="11">
+        <f>IF(J197="","",J197-K197)</f>
+      </c>
+      <c r="M197" s="11">
+        <f>IF(G197="","",G197-H197)</f>
+      </c>
+      <c r="N197" s="11">
+        <f>IF(M197="","",M197-I197)</f>
+      </c>
+      <c r="O197" s="11">
+        <f>IF(OR(L197="",L197&lt;=0),"자본잠식",ROUND(K197/L197*100,1))</f>
+      </c>
+      <c r="P197" s="11">
+        <f>IF(OR(L197="",L197&lt;=0),"—",ROUND(N197/L197*100,1))</f>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="7"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="7"/>
+      <c r="D198" s="7"/>
+      <c r="E198" s="7"/>
+      <c r="F198" s="7"/>
+      <c r="G198" s="7"/>
+      <c r="H198" s="7"/>
+      <c r="I198" s="7"/>
+      <c r="J198" s="11">
+        <f>IF(C198="","",C198+D198)</f>
+      </c>
+      <c r="K198" s="11">
+        <f>IF(E198="","",E198+F198)</f>
+      </c>
+      <c r="L198" s="11">
+        <f>IF(J198="","",J198-K198)</f>
+      </c>
+      <c r="M198" s="11">
+        <f>IF(G198="","",G198-H198)</f>
+      </c>
+      <c r="N198" s="11">
+        <f>IF(M198="","",M198-I198)</f>
+      </c>
+      <c r="O198" s="11">
+        <f>IF(OR(L198="",L198&lt;=0),"자본잠식",ROUND(K198/L198*100,1))</f>
+      </c>
+      <c r="P198" s="11">
+        <f>IF(OR(L198="",L198&lt;=0),"—",ROUND(N198/L198*100,1))</f>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="7"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="7"/>
+      <c r="D199" s="7"/>
+      <c r="E199" s="7"/>
+      <c r="F199" s="7"/>
+      <c r="G199" s="7"/>
+      <c r="H199" s="7"/>
+      <c r="I199" s="7"/>
+      <c r="J199" s="11">
+        <f>IF(C199="","",C199+D199)</f>
+      </c>
+      <c r="K199" s="11">
+        <f>IF(E199="","",E199+F199)</f>
+      </c>
+      <c r="L199" s="11">
+        <f>IF(J199="","",J199-K199)</f>
+      </c>
+      <c r="M199" s="11">
+        <f>IF(G199="","",G199-H199)</f>
+      </c>
+      <c r="N199" s="11">
+        <f>IF(M199="","",M199-I199)</f>
+      </c>
+      <c r="O199" s="11">
+        <f>IF(OR(L199="",L199&lt;=0),"자본잠식",ROUND(K199/L199*100,1))</f>
+      </c>
+      <c r="P199" s="11">
+        <f>IF(OR(L199="",L199&lt;=0),"—",ROUND(N199/L199*100,1))</f>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="7"/>
+      <c r="B200" s="7"/>
+      <c r="C200" s="7"/>
+      <c r="D200" s="7"/>
+      <c r="E200" s="7"/>
+      <c r="F200" s="7"/>
+      <c r="G200" s="7"/>
+      <c r="H200" s="7"/>
+      <c r="I200" s="7"/>
+      <c r="J200" s="11">
+        <f>IF(C200="","",C200+D200)</f>
+      </c>
+      <c r="K200" s="11">
+        <f>IF(E200="","",E200+F200)</f>
+      </c>
+      <c r="L200" s="11">
+        <f>IF(J200="","",J200-K200)</f>
+      </c>
+      <c r="M200" s="11">
+        <f>IF(G200="","",G200-H200)</f>
+      </c>
+      <c r="N200" s="11">
+        <f>IF(M200="","",M200-I200)</f>
+      </c>
+      <c r="O200" s="11">
+        <f>IF(OR(L200="",L200&lt;=0),"자본잠식",ROUND(K200/L200*100,1))</f>
+      </c>
+      <c r="P200" s="11">
+        <f>IF(OR(L200="",L200&lt;=0),"—",ROUND(N200/L200*100,1))</f>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="종목ID 확인" error="종목 시트에 적은 ID 중에서 고르세요." sqref="A5:A200">
+      <formula1>종목!$A$5:$A$50</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7886,7 +11232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8432,6 +11778,188 @@
           <t>S01</t>
         </is>
       </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -8452,7 +11980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8735,6 +12263,1576 @@
         <v>2750</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>★ 등락률 (자동 계산 · 참고용 — 힌트 방향 근거)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>종목 시트에 가격을 넣으면 연도별 등락률이 자동 계산돼요. 힌트 방향(호재·악재) 정할 때 근거로 보세요. 이 시트는 자동이라 채우지 않습니다. (가격을 %로 넣은 칸은 —로 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>종목ID</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>2020→2021</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>2021→2022</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>2022→2023</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>2023→2024</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>2024→2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="str">
+        <f>IF(종목!A5="","",종목!A5)</f>
+        <v>S01</v>
+      </c>
+      <c r="B5" s="11" t="str">
+        <f>IF(종목!B5="","",종목!B5)</f>
+        <v>승주보험</v>
+      </c>
+      <c r="C5" s="11" t="str">
+        <f>IF(종목!$A5="","",IF(종목!G5="","상장/정지",IF(종목!G5=0,"폐지(-100%)",IF(OR(종목!F5="",종목!F5=0),"신규상장",IFERROR(TEXT(종목!G5/종목!F5-1,"+0%;-0%"),"—")))))</f>
+        <v>+19%</v>
+      </c>
+      <c r="D5" s="11" t="str">
+        <f>IF(종목!$A5="","",IF(종목!H5="","상장/정지",IF(종목!H5=0,"폐지(-100%)",IF(OR(종목!G5="",종목!G5=0),"신규상장",IFERROR(TEXT(종목!H5/종목!G5-1,"+0%;-0%"),"—")))))</f>
+        <v>+43%</v>
+      </c>
+      <c r="E5" s="11" t="str">
+        <f>IF(종목!$A5="","",IF(종목!I5="","상장/정지",IF(종목!I5=0,"폐지(-100%)",IF(OR(종목!H5="",종목!H5=0),"신규상장",IFERROR(TEXT(종목!I5/종목!H5-1,"+0%;-0%"),"—")))))</f>
+        <v>+6%</v>
+      </c>
+      <c r="F5" s="11" t="str">
+        <f>IF(종목!$A5="","",IF(종목!J5="","상장/정지",IF(종목!J5=0,"폐지(-100%)",IF(OR(종목!I5="",종목!I5=0),"신규상장",IFERROR(TEXT(종목!J5/종목!I5-1,"+0%;-0%"),"—")))))</f>
+        <v>-1%</v>
+      </c>
+      <c r="G5" s="11" t="str">
+        <f>IF(종목!$A5="","",IF(종목!K5="","상장/정지",IF(종목!K5=0,"폐지(-100%)",IF(OR(종목!J5="",종목!J5=0),"신규상장",IFERROR(TEXT(종목!K5/종목!J5-1,"+0%;-0%"),"—")))))</f>
+        <v>-37%</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="str">
+        <f>IF(종목!A6="","",종목!A6)</f>
+        <v>S02</v>
+      </c>
+      <c r="B6" s="11" t="str">
+        <f>IF(종목!B6="","",종목!B6)</f>
+        <v>백만전자</v>
+      </c>
+      <c r="C6" s="11" t="str">
+        <f>IF(종목!$A6="","",IF(종목!G6="","상장/정지",IF(종목!G6=0,"폐지(-100%)",IF(OR(종목!F6="",종목!F6=0),"신규상장",IFERROR(TEXT(종목!G6/종목!F6-1,"+0%;-0%"),"—")))))</f>
+        <v>+81%</v>
+      </c>
+      <c r="D6" s="11" t="str">
+        <f>IF(종목!$A6="","",IF(종목!H6="","상장/정지",IF(종목!H6=0,"폐지(-100%)",IF(OR(종목!G6="",종목!G6=0),"신규상장",IFERROR(TEXT(종목!H6/종목!G6-1,"+0%;-0%"),"—")))))</f>
+        <v>+34%</v>
+      </c>
+      <c r="E6" s="11" t="str">
+        <f>IF(종목!$A6="","",IF(종목!I6="","상장/정지",IF(종목!I6=0,"폐지(-100%)",IF(OR(종목!H6="",종목!H6=0),"신규상장",IFERROR(TEXT(종목!I6/종목!H6-1,"+0%;-0%"),"—")))))</f>
+        <v>-27%</v>
+      </c>
+      <c r="F6" s="11" t="str">
+        <f>IF(종목!$A6="","",IF(종목!J6="","상장/정지",IF(종목!J6=0,"폐지(-100%)",IF(OR(종목!I6="",종목!I6=0),"신규상장",IFERROR(TEXT(종목!J6/종목!I6-1,"+0%;-0%"),"—")))))</f>
+        <v>+49%</v>
+      </c>
+      <c r="G6" s="11" t="str">
+        <f>IF(종목!$A6="","",IF(종목!K6="","상장/정지",IF(종목!K6=0,"폐지(-100%)",IF(OR(종목!J6="",종목!J6=0),"신규상장",IFERROR(TEXT(종목!K6/종목!J6-1,"+0%;-0%"),"—")))))</f>
+        <v>+30%</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="str">
+        <f>IF(종목!A7="","",종목!A7)</f>
+        <v>S03</v>
+      </c>
+      <c r="B7" s="11" t="str">
+        <f>IF(종목!B7="","",종목!B7)</f>
+        <v>C소프트</v>
+      </c>
+      <c r="C7" s="11" t="str">
+        <f>IF(종목!$A7="","",IF(종목!G7="","상장/정지",IF(종목!G7=0,"폐지(-100%)",IF(OR(종목!F7="",종목!F7=0),"신규상장",IFERROR(TEXT(종목!G7/종목!F7-1,"+0%;-0%"),"—")))))</f>
+        <v>+34%</v>
+      </c>
+      <c r="D7" s="11" t="str">
+        <f>IF(종목!$A7="","",IF(종목!H7="","상장/정지",IF(종목!H7=0,"폐지(-100%)",IF(OR(종목!G7="",종목!G7=0),"신규상장",IFERROR(TEXT(종목!H7/종목!G7-1,"+0%;-0%"),"—")))))</f>
+        <v>-8%</v>
+      </c>
+      <c r="E7" s="11" t="str">
+        <f>IF(종목!$A7="","",IF(종목!I7="","상장/정지",IF(종목!I7=0,"폐지(-100%)",IF(OR(종목!H7="",종목!H7=0),"신규상장",IFERROR(TEXT(종목!I7/종목!H7-1,"+0%;-0%"),"—")))))</f>
+        <v>-7%</v>
+      </c>
+      <c r="F7" s="11" t="str">
+        <f>IF(종목!$A7="","",IF(종목!J7="","상장/정지",IF(종목!J7=0,"폐지(-100%)",IF(OR(종목!I7="",종목!I7=0),"신규상장",IFERROR(TEXT(종목!J7/종목!I7-1,"+0%;-0%"),"—")))))</f>
+        <v>+11%</v>
+      </c>
+      <c r="G7" s="11" t="str">
+        <f>IF(종목!$A7="","",IF(종목!K7="","상장/정지",IF(종목!K7=0,"폐지(-100%)",IF(OR(종목!J7="",종목!J7=0),"신규상장",IFERROR(TEXT(종목!K7/종목!J7-1,"+0%;-0%"),"—")))))</f>
+        <v>+50%</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="str">
+        <f>IF(종목!A8="","",종목!A8)</f>
+        <v>S04</v>
+      </c>
+      <c r="B8" s="11" t="str">
+        <f>IF(종목!B8="","",종목!B8)</f>
+        <v>D게임즈</v>
+      </c>
+      <c r="C8" s="11" t="str">
+        <f>IF(종목!$A8="","",IF(종목!G8="","상장/정지",IF(종목!G8=0,"폐지(-100%)",IF(OR(종목!F8="",종목!F8=0),"신규상장",IFERROR(TEXT(종목!G8/종목!F8-1,"+0%;-0%"),"—")))))</f>
+        <v>+300%</v>
+      </c>
+      <c r="D8" s="11" t="str">
+        <f>IF(종목!$A8="","",IF(종목!H8="","상장/정지",IF(종목!H8=0,"폐지(-100%)",IF(OR(종목!G8="",종목!G8=0),"신규상장",IFERROR(TEXT(종목!H8/종목!G8-1,"+0%;-0%"),"—")))))</f>
+        <v>+825%</v>
+      </c>
+      <c r="E8" s="11" t="str">
+        <f>IF(종목!$A8="","",IF(종목!I8="","상장/정지",IF(종목!I8=0,"폐지(-100%)",IF(OR(종목!H8="",종목!H8=0),"신규상장",IFERROR(TEXT(종목!I8/종목!H8-1,"+0%;-0%"),"—")))))</f>
+        <v>-51%</v>
+      </c>
+      <c r="F8" s="11" t="str">
+        <f>IF(종목!$A8="","",IF(종목!J8="","상장/정지",IF(종목!J8=0,"폐지(-100%)",IF(OR(종목!I8="",종목!I8=0),"신규상장",IFERROR(TEXT(종목!J8/종목!I8-1,"+0%;-0%"),"—")))))</f>
+        <v>-6%</v>
+      </c>
+      <c r="G8" s="11" t="str">
+        <f>IF(종목!$A8="","",IF(종목!K8="","상장/정지",IF(종목!K8=0,"폐지(-100%)",IF(OR(종목!J8="",종목!J8=0),"신규상장",IFERROR(TEXT(종목!K8/종목!J8-1,"+0%;-0%"),"—")))))</f>
+        <v>+82%</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="str">
+        <f>IF(종목!A9="","",종목!A9)</f>
+        <v>S05</v>
+      </c>
+      <c r="B9" s="11" t="str">
+        <f>IF(종목!B9="","",종목!B9)</f>
+        <v>양재금융</v>
+      </c>
+      <c r="C9" s="11" t="str">
+        <f>IF(종목!$A9="","",IF(종목!G9="","상장/정지",IF(종목!G9=0,"폐지(-100%)",IF(OR(종목!F9="",종목!F9=0),"신규상장",IFERROR(TEXT(종목!G9/종목!F9-1,"+0%;-0%"),"—")))))</f>
+        <v>+55%</v>
+      </c>
+      <c r="D9" s="11" t="str">
+        <f>IF(종목!$A9="","",IF(종목!H9="","상장/정지",IF(종목!H9=0,"폐지(-100%)",IF(OR(종목!G9="",종목!G9=0),"신규상장",IFERROR(TEXT(종목!H9/종목!G9-1,"+0%;-0%"),"—")))))</f>
+        <v>+75%</v>
+      </c>
+      <c r="E9" s="11" t="str">
+        <f>IF(종목!$A9="","",IF(종목!I9="","상장/정지",IF(종목!I9=0,"폐지(-100%)",IF(OR(종목!H9="",종목!H9=0),"신규상장",IFERROR(TEXT(종목!I9/종목!H9-1,"+0%;-0%"),"—")))))</f>
+        <v>-54%</v>
+      </c>
+      <c r="F9" s="11" t="str">
+        <f>IF(종목!$A9="","",IF(종목!J9="","상장/정지",IF(종목!J9=0,"폐지(-100%)",IF(OR(종목!I9="",종목!I9=0),"신규상장",IFERROR(TEXT(종목!J9/종목!I9-1,"+0%;-0%"),"—")))))</f>
+        <v>상장/정지</v>
+      </c>
+      <c r="G9" s="11" t="str">
+        <f>IF(종목!$A9="","",IF(종목!K9="","상장/정지",IF(종목!K9=0,"폐지(-100%)",IF(OR(종목!J9="",종목!J9=0),"신규상장",IFERROR(TEXT(종목!K9/종목!J9-1,"+0%;-0%"),"—")))))</f>
+        <v>상장/정지</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="str">
+        <f>IF(종목!A10="","",종목!A10)</f>
+        <v>S06</v>
+      </c>
+      <c r="B10" s="11" t="str">
+        <f>IF(종목!B10="","",종목!B10)</f>
+        <v>F모빌리티</v>
+      </c>
+      <c r="C10" s="11" t="str">
+        <f>IF(종목!$A10="","",IF(종목!G10="","상장/정지",IF(종목!G10=0,"폐지(-100%)",IF(OR(종목!F10="",종목!F10=0),"신규상장",IFERROR(TEXT(종목!G10/종목!F10-1,"+0%;-0%"),"—")))))</f>
+        <v>+507%</v>
+      </c>
+      <c r="D10" s="11" t="str">
+        <f>IF(종목!$A10="","",IF(종목!H10="","상장/정지",IF(종목!H10=0,"폐지(-100%)",IF(OR(종목!G10="",종목!G10=0),"신규상장",IFERROR(TEXT(종목!H10/종목!G10-1,"+0%;-0%"),"—")))))</f>
+        <v>-75%</v>
+      </c>
+      <c r="E10" s="11" t="str">
+        <f>IF(종목!$A10="","",IF(종목!I10="","상장/정지",IF(종목!I10=0,"폐지(-100%)",IF(OR(종목!H10="",종목!H10=0),"신규상장",IFERROR(TEXT(종목!I10/종목!H10-1,"+0%;-0%"),"—")))))</f>
+        <v>-62%</v>
+      </c>
+      <c r="F10" s="11" t="str">
+        <f>IF(종목!$A10="","",IF(종목!J10="","상장/정지",IF(종목!J10=0,"폐지(-100%)",IF(OR(종목!I10="",종목!I10=0),"신규상장",IFERROR(TEXT(종목!J10/종목!I10-1,"+0%;-0%"),"—")))))</f>
+        <v>-80%</v>
+      </c>
+      <c r="G10" s="11" t="str">
+        <f>IF(종목!$A10="","",IF(종목!K10="","상장/정지",IF(종목!K10=0,"폐지(-100%)",IF(OR(종목!J10="",종목!J10=0),"신규상장",IFERROR(TEXT(종목!K10/종목!J10-1,"+0%;-0%"),"—")))))</f>
+        <v>상장/정지</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="str">
+        <f>IF(종목!A11="","",종목!A11)</f>
+        <v>S07</v>
+      </c>
+      <c r="B11" s="11" t="str">
+        <f>IF(종목!B11="","",종목!B11)</f>
+        <v>형록전자</v>
+      </c>
+      <c r="C11" s="11" t="str">
+        <f>IF(종목!$A11="","",IF(종목!G11="","상장/정지",IF(종목!G11=0,"폐지(-100%)",IF(OR(종목!F11="",종목!F11=0),"신규상장",IFERROR(TEXT(종목!G11/종목!F11-1,"+0%;-0%"),"—")))))</f>
+        <v>-17%</v>
+      </c>
+      <c r="D11" s="11" t="str">
+        <f>IF(종목!$A11="","",IF(종목!H11="","상장/정지",IF(종목!H11=0,"폐지(-100%)",IF(OR(종목!G11="",종목!G11=0),"신규상장",IFERROR(TEXT(종목!H11/종목!G11-1,"+0%;-0%"),"—")))))</f>
+        <v>+4%</v>
+      </c>
+      <c r="E11" s="11" t="str">
+        <f>IF(종목!$A11="","",IF(종목!I11="","상장/정지",IF(종목!I11=0,"폐지(-100%)",IF(OR(종목!H11="",종목!H11=0),"신규상장",IFERROR(TEXT(종목!I11/종목!H11-1,"+0%;-0%"),"—")))))</f>
+        <v>-49%</v>
+      </c>
+      <c r="F11" s="11" t="str">
+        <f>IF(종목!$A11="","",IF(종목!J11="","상장/정지",IF(종목!J11=0,"폐지(-100%)",IF(OR(종목!I11="",종목!I11=0),"신규상장",IFERROR(TEXT(종목!J11/종목!I11-1,"+0%;-0%"),"—")))))</f>
+        <v>+92%</v>
+      </c>
+      <c r="G11" s="11" t="str">
+        <f>IF(종목!$A11="","",IF(종목!K11="","상장/정지",IF(종목!K11=0,"폐지(-100%)",IF(OR(종목!J11="",종목!J11=0),"신규상장",IFERROR(TEXT(종목!K11/종목!J11-1,"+0%;-0%"),"—")))))</f>
+        <v>-60%</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="str">
+        <f>IF(종목!A12="","",종목!A12)</f>
+        <v>S08</v>
+      </c>
+      <c r="B12" s="11" t="str">
+        <f>IF(종목!B12="","",종목!B12)</f>
+        <v>백학푸드</v>
+      </c>
+      <c r="C12" s="11" t="str">
+        <f>IF(종목!$A12="","",IF(종목!G12="","상장/정지",IF(종목!G12=0,"폐지(-100%)",IF(OR(종목!F12="",종목!F12=0),"신규상장",IFERROR(TEXT(종목!G12/종목!F12-1,"+0%;-0%"),"—")))))</f>
+        <v>-2%</v>
+      </c>
+      <c r="D12" s="11" t="str">
+        <f>IF(종목!$A12="","",IF(종목!H12="","상장/정지",IF(종목!H12=0,"폐지(-100%)",IF(OR(종목!G12="",종목!G12=0),"신규상장",IFERROR(TEXT(종목!H12/종목!G12-1,"+0%;-0%"),"—")))))</f>
+        <v>+9%</v>
+      </c>
+      <c r="E12" s="11" t="str">
+        <f>IF(종목!$A12="","",IF(종목!I12="","상장/정지",IF(종목!I12=0,"폐지(-100%)",IF(OR(종목!H12="",종목!H12=0),"신규상장",IFERROR(TEXT(종목!I12/종목!H12-1,"+0%;-0%"),"—")))))</f>
+        <v>+7%</v>
+      </c>
+      <c r="F12" s="11" t="str">
+        <f>IF(종목!$A12="","",IF(종목!J12="","상장/정지",IF(종목!J12=0,"폐지(-100%)",IF(OR(종목!I12="",종목!I12=0),"신규상장",IFERROR(TEXT(종목!J12/종목!I12-1,"+0%;-0%"),"—")))))</f>
+        <v>-8%</v>
+      </c>
+      <c r="G12" s="11" t="str">
+        <f>IF(종목!$A12="","",IF(종목!K12="","상장/정지",IF(종목!K12=0,"폐지(-100%)",IF(OR(종목!J12="",종목!J12=0),"신규상장",IFERROR(TEXT(종목!K12/종목!J12-1,"+0%;-0%"),"—")))))</f>
+        <v>+7%</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="str">
+        <f>IF(종목!A13="","",종목!A13)</f>
+        <v>S09</v>
+      </c>
+      <c r="B13" s="11" t="str">
+        <f>IF(종목!B13="","",종목!B13)</f>
+        <v>I모터스</v>
+      </c>
+      <c r="C13" s="11" t="str">
+        <f>IF(종목!$A13="","",IF(종목!G13="","상장/정지",IF(종목!G13=0,"폐지(-100%)",IF(OR(종목!F13="",종목!F13=0),"신규상장",IFERROR(TEXT(종목!G13/종목!F13-1,"+0%;-0%"),"—")))))</f>
+        <v>+770%</v>
+      </c>
+      <c r="D13" s="11" t="str">
+        <f>IF(종목!$A13="","",IF(종목!H13="","상장/정지",IF(종목!H13=0,"폐지(-100%)",IF(OR(종목!G13="",종목!G13=0),"신규상장",IFERROR(TEXT(종목!H13/종목!G13-1,"+0%;-0%"),"—")))))</f>
+        <v>+50%</v>
+      </c>
+      <c r="E13" s="11" t="str">
+        <f>IF(종목!$A13="","",IF(종목!I13="","상장/정지",IF(종목!I13=0,"폐지(-100%)",IF(OR(종목!H13="",종목!H13=0),"신규상장",IFERROR(TEXT(종목!I13/종목!H13-1,"+0%;-0%"),"—")))))</f>
+        <v>-65%</v>
+      </c>
+      <c r="F13" s="11" t="str">
+        <f>IF(종목!$A13="","",IF(종목!J13="","상장/정지",IF(종목!J13=0,"폐지(-100%)",IF(OR(종목!I13="",종목!I13=0),"신규상장",IFERROR(TEXT(종목!J13/종목!I13-1,"+0%;-0%"),"—")))))</f>
+        <v>+102%</v>
+      </c>
+      <c r="G13" s="11" t="str">
+        <f>IF(종목!$A13="","",IF(종목!K13="","상장/정지",IF(종목!K13=0,"폐지(-100%)",IF(OR(종목!J13="",종목!J13=0),"신규상장",IFERROR(TEXT(종목!K13/종목!J13-1,"+0%;-0%"),"—")))))</f>
+        <v>+63%</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="str">
+        <f>IF(종목!A14="","",종목!A14)</f>
+        <v>S10</v>
+      </c>
+      <c r="B14" s="11" t="str">
+        <f>IF(종목!B14="","",종목!B14)</f>
+        <v>J시스템즈</v>
+      </c>
+      <c r="C14" s="11" t="str">
+        <f>IF(종목!$A14="","",IF(종목!G14="","상장/정지",IF(종목!G14=0,"폐지(-100%)",IF(OR(종목!F14="",종목!F14=0),"신규상장",IFERROR(TEXT(종목!G14/종목!F14-1,"+0%;-0%"),"—")))))</f>
+        <v>+50%</v>
+      </c>
+      <c r="D14" s="11" t="str">
+        <f>IF(종목!$A14="","",IF(종목!H14="","상장/정지",IF(종목!H14=0,"폐지(-100%)",IF(OR(종목!G14="",종목!G14=0),"신규상장",IFERROR(TEXT(종목!H14/종목!G14-1,"+0%;-0%"),"—")))))</f>
+        <v>+33%</v>
+      </c>
+      <c r="E14" s="11" t="str">
+        <f>IF(종목!$A14="","",IF(종목!I14="","상장/정지",IF(종목!I14=0,"폐지(-100%)",IF(OR(종목!H14="",종목!H14=0),"신규상장",IFERROR(TEXT(종목!I14/종목!H14-1,"+0%;-0%"),"—")))))</f>
+        <v>+50%</v>
+      </c>
+      <c r="F14" s="11" t="str">
+        <f>IF(종목!$A14="","",IF(종목!J14="","상장/정지",IF(종목!J14=0,"폐지(-100%)",IF(OR(종목!I14="",종목!I14=0),"신규상장",IFERROR(TEXT(종목!J14/종목!I14-1,"+0%;-0%"),"—")))))</f>
+        <v>+1067%</v>
+      </c>
+      <c r="G14" s="11" t="str">
+        <f>IF(종목!$A14="","",IF(종목!K14="","상장/정지",IF(종목!K14=0,"폐지(-100%)",IF(OR(종목!J14="",종목!J14=0),"신규상장",IFERROR(TEXT(종목!K14/종목!J14-1,"+0%;-0%"),"—")))))</f>
+        <v>-69%</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="str">
+        <f>IF(종목!A15="","",종목!A15)</f>
+        <v>S11</v>
+      </c>
+      <c r="B15" s="11" t="str">
+        <f>IF(종목!B15="","",종목!B15)</f>
+        <v>경상제약</v>
+      </c>
+      <c r="C15" s="11" t="str">
+        <f>IF(종목!$A15="","",IF(종목!G15="","상장/정지",IF(종목!G15=0,"폐지(-100%)",IF(OR(종목!F15="",종목!F15=0),"신규상장",IFERROR(TEXT(종목!G15/종목!F15-1,"+0%;-0%"),"—")))))</f>
+        <v>+21%</v>
+      </c>
+      <c r="D15" s="11" t="str">
+        <f>IF(종목!$A15="","",IF(종목!H15="","상장/정지",IF(종목!H15=0,"폐지(-100%)",IF(OR(종목!G15="",종목!G15=0),"신규상장",IFERROR(TEXT(종목!H15/종목!G15-1,"+0%;-0%"),"—")))))</f>
+        <v>+65%</v>
+      </c>
+      <c r="E15" s="11" t="str">
+        <f>IF(종목!$A15="","",IF(종목!I15="","상장/정지",IF(종목!I15=0,"폐지(-100%)",IF(OR(종목!H15="",종목!H15=0),"신규상장",IFERROR(TEXT(종목!I15/종목!H15-1,"+0%;-0%"),"—")))))</f>
+        <v>+20%</v>
+      </c>
+      <c r="F15" s="11" t="str">
+        <f>IF(종목!$A15="","",IF(종목!J15="","상장/정지",IF(종목!J15=0,"폐지(-100%)",IF(OR(종목!I15="",종목!I15=0),"신규상장",IFERROR(TEXT(종목!J15/종목!I15-1,"+0%;-0%"),"—")))))</f>
+        <v>+54%</v>
+      </c>
+      <c r="G15" s="11" t="str">
+        <f>IF(종목!$A15="","",IF(종목!K15="","상장/정지",IF(종목!K15=0,"폐지(-100%)",IF(OR(종목!J15="",종목!J15=0),"신규상장",IFERROR(TEXT(종목!K15/종목!J15-1,"+0%;-0%"),"—")))))</f>
+        <v>-17%</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="str">
+        <f>IF(종목!A16="","",종목!A16)</f>
+        <v>S12</v>
+      </c>
+      <c r="B16" s="11" t="str">
+        <f>IF(종목!B16="","",종목!B16)</f>
+        <v>HeeSoo ENT.</v>
+      </c>
+      <c r="C16" s="11" t="str">
+        <f>IF(종목!$A16="","",IF(종목!G16="","상장/정지",IF(종목!G16=0,"폐지(-100%)",IF(OR(종목!F16="",종목!F16=0),"신규상장",IFERROR(TEXT(종목!G16/종목!F16-1,"+0%;-0%"),"—")))))</f>
+        <v>+69%</v>
+      </c>
+      <c r="D16" s="11" t="str">
+        <f>IF(종목!$A16="","",IF(종목!H16="","상장/정지",IF(종목!H16=0,"폐지(-100%)",IF(OR(종목!G16="",종목!G16=0),"신규상장",IFERROR(TEXT(종목!H16/종목!G16-1,"+0%;-0%"),"—")))))</f>
+        <v>+11%</v>
+      </c>
+      <c r="E16" s="11" t="str">
+        <f>IF(종목!$A16="","",IF(종목!I16="","상장/정지",IF(종목!I16=0,"폐지(-100%)",IF(OR(종목!H16="",종목!H16=0),"신규상장",IFERROR(TEXT(종목!I16/종목!H16-1,"+0%;-0%"),"—")))))</f>
+        <v>-52%</v>
+      </c>
+      <c r="F16" s="11" t="str">
+        <f>IF(종목!$A16="","",IF(종목!J16="","상장/정지",IF(종목!J16=0,"폐지(-100%)",IF(OR(종목!I16="",종목!I16=0),"신규상장",IFERROR(TEXT(종목!J16/종목!I16-1,"+0%;-0%"),"—")))))</f>
+        <v>+66%</v>
+      </c>
+      <c r="G16" s="11" t="str">
+        <f>IF(종목!$A16="","",IF(종목!K16="","상장/정지",IF(종목!K16=0,"폐지(-100%)",IF(OR(종목!J16="",종목!J16=0),"신규상장",IFERROR(TEXT(종목!K16/종목!J16-1,"+0%;-0%"),"—")))))</f>
+        <v>+85%</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="str">
+        <f>IF(종목!A17="","",종목!A17)</f>
+        <v>S13</v>
+      </c>
+      <c r="B17" s="11" t="str">
+        <f>IF(종목!B17="","",종목!B17)</f>
+        <v>M증권</v>
+      </c>
+      <c r="C17" s="11" t="str">
+        <f>IF(종목!$A17="","",IF(종목!G17="","상장/정지",IF(종목!G17=0,"폐지(-100%)",IF(OR(종목!F17="",종목!F17=0),"신규상장",IFERROR(TEXT(종목!G17/종목!F17-1,"+0%;-0%"),"—")))))</f>
+        <v>상장/정지</v>
+      </c>
+      <c r="D17" s="11" t="str">
+        <f>IF(종목!$A17="","",IF(종목!H17="","상장/정지",IF(종목!H17=0,"폐지(-100%)",IF(OR(종목!G17="",종목!G17=0),"신규상장",IFERROR(TEXT(종목!H17/종목!G17-1,"+0%;-0%"),"—")))))</f>
+        <v>신규상장</v>
+      </c>
+      <c r="E17" s="11" t="str">
+        <f>IF(종목!$A17="","",IF(종목!I17="","상장/정지",IF(종목!I17=0,"폐지(-100%)",IF(OR(종목!H17="",종목!H17=0),"신규상장",IFERROR(TEXT(종목!I17/종목!H17-1,"+0%;-0%"),"—")))))</f>
+        <v>-53%</v>
+      </c>
+      <c r="F17" s="11" t="str">
+        <f>IF(종목!$A17="","",IF(종목!J17="","상장/정지",IF(종목!J17=0,"폐지(-100%)",IF(OR(종목!I17="",종목!I17=0),"신규상장",IFERROR(TEXT(종목!J17/종목!I17-1,"+0%;-0%"),"—")))))</f>
+        <v>+50%</v>
+      </c>
+      <c r="G17" s="11" t="str">
+        <f>IF(종목!$A17="","",IF(종목!K17="","상장/정지",IF(종목!K17=0,"폐지(-100%)",IF(OR(종목!J17="",종목!J17=0),"신규상장",IFERROR(TEXT(종목!K17/종목!J17-1,"+0%;-0%"),"—")))))</f>
+        <v>+208%</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="str">
+        <f>IF(종목!A18="","",종목!A18)</f>
+        <v>S14</v>
+      </c>
+      <c r="B18" s="11" t="str">
+        <f>IF(종목!B18="","",종목!B18)</f>
+        <v>N스포츠</v>
+      </c>
+      <c r="C18" s="11" t="str">
+        <f>IF(종목!$A18="","",IF(종목!G18="","상장/정지",IF(종목!G18=0,"폐지(-100%)",IF(OR(종목!F18="",종목!F18=0),"신규상장",IFERROR(TEXT(종목!G18/종목!F18-1,"+0%;-0%"),"—")))))</f>
+        <v>+439%</v>
+      </c>
+      <c r="D18" s="11" t="str">
+        <f>IF(종목!$A18="","",IF(종목!H18="","상장/정지",IF(종목!H18=0,"폐지(-100%)",IF(OR(종목!G18="",종목!G18=0),"신규상장",IFERROR(TEXT(종목!H18/종목!G18-1,"+0%;-0%"),"—")))))</f>
+        <v>-77%</v>
+      </c>
+      <c r="E18" s="11" t="str">
+        <f>IF(종목!$A18="","",IF(종목!I18="","상장/정지",IF(종목!I18=0,"폐지(-100%)",IF(OR(종목!H18="",종목!H18=0),"신규상장",IFERROR(TEXT(종목!I18/종목!H18-1,"+0%;-0%"),"—")))))</f>
+        <v>-80%</v>
+      </c>
+      <c r="F18" s="11" t="str">
+        <f>IF(종목!$A18="","",IF(종목!J18="","상장/정지",IF(종목!J18=0,"폐지(-100%)",IF(OR(종목!I18="",종목!I18=0),"신규상장",IFERROR(TEXT(종목!J18/종목!I18-1,"+0%;-0%"),"—")))))</f>
+        <v>-14%</v>
+      </c>
+      <c r="G18" s="11" t="str">
+        <f>IF(종목!$A18="","",IF(종목!K18="","상장/정지",IF(종목!K18=0,"폐지(-100%)",IF(OR(종목!J18="",종목!J18=0),"신규상장",IFERROR(TEXT(종목!K18/종목!J18-1,"+0%;-0%"),"—")))))</f>
+        <v>+33%</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="str">
+        <f>IF(종목!A19="","",종목!A19)</f>
+        <v>S15</v>
+      </c>
+      <c r="B19" s="11" t="str">
+        <f>IF(종목!B19="","",종목!B19)</f>
+        <v>O에어로</v>
+      </c>
+      <c r="C19" s="11" t="str">
+        <f>IF(종목!$A19="","",IF(종목!G19="","상장/정지",IF(종목!G19=0,"폐지(-100%)",IF(OR(종목!F19="",종목!F19=0),"신규상장",IFERROR(TEXT(종목!G19/종목!F19-1,"+0%;-0%"),"—")))))</f>
+        <v>-34%</v>
+      </c>
+      <c r="D19" s="11" t="str">
+        <f>IF(종목!$A19="","",IF(종목!H19="","상장/정지",IF(종목!H19=0,"폐지(-100%)",IF(OR(종목!G19="",종목!G19=0),"신규상장",IFERROR(TEXT(종목!H19/종목!G19-1,"+0%;-0%"),"—")))))</f>
+        <v>-6%</v>
+      </c>
+      <c r="E19" s="11" t="str">
+        <f>IF(종목!$A19="","",IF(종목!I19="","상장/정지",IF(종목!I19=0,"폐지(-100%)",IF(OR(종목!H19="",종목!H19=0),"신규상장",IFERROR(TEXT(종목!I19/종목!H19-1,"+0%;-0%"),"—")))))</f>
+        <v>-5%</v>
+      </c>
+      <c r="F19" s="11" t="str">
+        <f>IF(종목!$A19="","",IF(종목!J19="","상장/정지",IF(종목!J19=0,"폐지(-100%)",IF(OR(종목!I19="",종목!I19=0),"신규상장",IFERROR(TEXT(종목!J19/종목!I19-1,"+0%;-0%"),"—")))))</f>
+        <v>+37%</v>
+      </c>
+      <c r="G19" s="11" t="str">
+        <f>IF(종목!$A19="","",IF(종목!K19="","상장/정지",IF(종목!K19=0,"폐지(-100%)",IF(OR(종목!J19="",종목!J19=0),"신규상장",IFERROR(TEXT(종목!K19/종목!J19-1,"+0%;-0%"),"—")))))</f>
+        <v>-32%</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="str">
+        <f>IF(종목!A20="","",종목!A20)</f>
+        <v>S16</v>
+      </c>
+      <c r="B20" s="11" t="str">
+        <f>IF(종목!B20="","",종목!B20)</f>
+        <v>윤선바이오</v>
+      </c>
+      <c r="C20" s="11" t="str">
+        <f>IF(종목!$A20="","",IF(종목!G20="","상장/정지",IF(종목!G20=0,"폐지(-100%)",IF(OR(종목!F20="",종목!F20=0),"신규상장",IFERROR(TEXT(종목!G20/종목!F20-1,"+0%;-0%"),"—")))))</f>
+        <v>+447%</v>
+      </c>
+      <c r="D20" s="11" t="str">
+        <f>IF(종목!$A20="","",IF(종목!H20="","상장/정지",IF(종목!H20=0,"폐지(-100%)",IF(OR(종목!G20="",종목!G20=0),"신규상장",IFERROR(TEXT(종목!H20/종목!G20-1,"+0%;-0%"),"—")))))</f>
+        <v>+143%</v>
+      </c>
+      <c r="E20" s="11" t="str">
+        <f>IF(종목!$A20="","",IF(종목!I20="","상장/정지",IF(종목!I20=0,"폐지(-100%)",IF(OR(종목!H20="",종목!H20=0),"신규상장",IFERROR(TEXT(종목!I20/종목!H20-1,"+0%;-0%"),"—")))))</f>
+        <v>-29%</v>
+      </c>
+      <c r="F20" s="11" t="str">
+        <f>IF(종목!$A20="","",IF(종목!J20="","상장/정지",IF(종목!J20=0,"폐지(-100%)",IF(OR(종목!I20="",종목!I20=0),"신규상장",IFERROR(TEXT(종목!J20/종목!I20-1,"+0%;-0%"),"—")))))</f>
+        <v>-45%</v>
+      </c>
+      <c r="G20" s="11" t="str">
+        <f>IF(종목!$A20="","",IF(종목!K20="","상장/정지",IF(종목!K20=0,"폐지(-100%)",IF(OR(종목!J20="",종목!J20=0),"신규상장",IFERROR(TEXT(종목!K20/종목!J20-1,"+0%;-0%"),"—")))))</f>
+        <v>-59%</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="str">
+        <f>IF(종목!A21="","",종목!A21)</f>
+        <v>S17</v>
+      </c>
+      <c r="B21" s="11" t="str">
+        <f>IF(종목!B21="","",종목!B21)</f>
+        <v>큐픽플랫폼</v>
+      </c>
+      <c r="C21" s="11" t="str">
+        <f>IF(종목!$A21="","",IF(종목!G21="","상장/정지",IF(종목!G21=0,"폐지(-100%)",IF(OR(종목!F21="",종목!F21=0),"신규상장",IFERROR(TEXT(종목!G21/종목!F21-1,"+0%;-0%"),"—")))))</f>
+        <v>+161%</v>
+      </c>
+      <c r="D21" s="11" t="str">
+        <f>IF(종목!$A21="","",IF(종목!H21="","상장/정지",IF(종목!H21=0,"폐지(-100%)",IF(OR(종목!G21="",종목!G21=0),"신규상장",IFERROR(TEXT(종목!H21/종목!G21-1,"+0%;-0%"),"—")))))</f>
+        <v>-2%</v>
+      </c>
+      <c r="E21" s="11" t="str">
+        <f>IF(종목!$A21="","",IF(종목!I21="","상장/정지",IF(종목!I21=0,"폐지(-100%)",IF(OR(종목!H21="",종목!H21=0),"신규상장",IFERROR(TEXT(종목!I21/종목!H21-1,"+0%;-0%"),"—")))))</f>
+        <v>-98%</v>
+      </c>
+      <c r="F21" s="11" t="str">
+        <f>IF(종목!$A21="","",IF(종목!J21="","상장/정지",IF(종목!J21=0,"폐지(-100%)",IF(OR(종목!I21="",종목!I21=0),"신규상장",IFERROR(TEXT(종목!J21/종목!I21-1,"+0%;-0%"),"—")))))</f>
+        <v>+900%</v>
+      </c>
+      <c r="G21" s="11" t="str">
+        <f>IF(종목!$A21="","",IF(종목!K21="","상장/정지",IF(종목!K21=0,"폐지(-100%)",IF(OR(종목!J21="",종목!J21=0),"신규상장",IFERROR(TEXT(종목!K21/종목!J21-1,"+0%;-0%"),"—")))))</f>
+        <v>+300%</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="str">
+        <f>IF(종목!A22="","",종목!A22)</f>
+        <v>S18</v>
+      </c>
+      <c r="B22" s="11" t="str">
+        <f>IF(종목!B22="","",종목!B22)</f>
+        <v>하프케이</v>
+      </c>
+      <c r="C22" s="11" t="str">
+        <f>IF(종목!$A22="","",IF(종목!G22="","상장/정지",IF(종목!G22=0,"폐지(-100%)",IF(OR(종목!F22="",종목!F22=0),"신규상장",IFERROR(TEXT(종목!G22/종목!F22-1,"+0%;-0%"),"—")))))</f>
+        <v>+16%</v>
+      </c>
+      <c r="D22" s="11" t="str">
+        <f>IF(종목!$A22="","",IF(종목!H22="","상장/정지",IF(종목!H22=0,"폐지(-100%)",IF(OR(종목!G22="",종목!G22=0),"신규상장",IFERROR(TEXT(종목!H22/종목!G22-1,"+0%;-0%"),"—")))))</f>
+        <v>+27%</v>
+      </c>
+      <c r="E22" s="11" t="str">
+        <f>IF(종목!$A22="","",IF(종목!I22="","상장/정지",IF(종목!I22=0,"폐지(-100%)",IF(OR(종목!H22="",종목!H22=0),"신규상장",IFERROR(TEXT(종목!I22/종목!H22-1,"+0%;-0%"),"—")))))</f>
+        <v>-19%</v>
+      </c>
+      <c r="F22" s="11" t="str">
+        <f>IF(종목!$A22="","",IF(종목!J22="","상장/정지",IF(종목!J22=0,"폐지(-100%)",IF(OR(종목!I22="",종목!I22=0),"신규상장",IFERROR(TEXT(종목!J22/종목!I22-1,"+0%;-0%"),"—")))))</f>
+        <v>+24%</v>
+      </c>
+      <c r="G22" s="11" t="str">
+        <f>IF(종목!$A22="","",IF(종목!K22="","상장/정지",IF(종목!K22=0,"폐지(-100%)",IF(OR(종목!J22="",종목!J22=0),"신규상장",IFERROR(TEXT(종목!K22/종목!J22-1,"+0%;-0%"),"—")))))</f>
+        <v>+23%</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="str">
+        <f>IF(종목!A23="","",종목!A23)</f>
+        <v/>
+      </c>
+      <c r="B23" s="11" t="str">
+        <f>IF(종목!B23="","",종목!B23)</f>
+        <v/>
+      </c>
+      <c r="C23" s="11" t="str">
+        <f>IF(종목!$A23="","",IF(종목!G23="","상장/정지",IF(종목!G23=0,"폐지(-100%)",IF(OR(종목!F23="",종목!F23=0),"신규상장",IFERROR(TEXT(종목!G23/종목!F23-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D23" s="11" t="str">
+        <f>IF(종목!$A23="","",IF(종목!H23="","상장/정지",IF(종목!H23=0,"폐지(-100%)",IF(OR(종목!G23="",종목!G23=0),"신규상장",IFERROR(TEXT(종목!H23/종목!G23-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="11" t="str">
+        <f>IF(종목!$A23="","",IF(종목!I23="","상장/정지",IF(종목!I23=0,"폐지(-100%)",IF(OR(종목!H23="",종목!H23=0),"신규상장",IFERROR(TEXT(종목!I23/종목!H23-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F23" s="11" t="str">
+        <f>IF(종목!$A23="","",IF(종목!J23="","상장/정지",IF(종목!J23=0,"폐지(-100%)",IF(OR(종목!I23="",종목!I23=0),"신규상장",IFERROR(TEXT(종목!J23/종목!I23-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G23" s="11" t="str">
+        <f>IF(종목!$A23="","",IF(종목!K23="","상장/정지",IF(종목!K23=0,"폐지(-100%)",IF(OR(종목!J23="",종목!J23=0),"신규상장",IFERROR(TEXT(종목!K23/종목!J23-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="str">
+        <f>IF(종목!A24="","",종목!A24)</f>
+        <v/>
+      </c>
+      <c r="B24" s="11" t="str">
+        <f>IF(종목!B24="","",종목!B24)</f>
+        <v/>
+      </c>
+      <c r="C24" s="11" t="str">
+        <f>IF(종목!$A24="","",IF(종목!G24="","상장/정지",IF(종목!G24=0,"폐지(-100%)",IF(OR(종목!F24="",종목!F24=0),"신규상장",IFERROR(TEXT(종목!G24/종목!F24-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D24" s="11" t="str">
+        <f>IF(종목!$A24="","",IF(종목!H24="","상장/정지",IF(종목!H24=0,"폐지(-100%)",IF(OR(종목!G24="",종목!G24=0),"신규상장",IFERROR(TEXT(종목!H24/종목!G24-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="11" t="str">
+        <f>IF(종목!$A24="","",IF(종목!I24="","상장/정지",IF(종목!I24=0,"폐지(-100%)",IF(OR(종목!H24="",종목!H24=0),"신규상장",IFERROR(TEXT(종목!I24/종목!H24-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F24" s="11" t="str">
+        <f>IF(종목!$A24="","",IF(종목!J24="","상장/정지",IF(종목!J24=0,"폐지(-100%)",IF(OR(종목!I24="",종목!I24=0),"신규상장",IFERROR(TEXT(종목!J24/종목!I24-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G24" s="11" t="str">
+        <f>IF(종목!$A24="","",IF(종목!K24="","상장/정지",IF(종목!K24=0,"폐지(-100%)",IF(OR(종목!J24="",종목!J24=0),"신규상장",IFERROR(TEXT(종목!K24/종목!J24-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="str">
+        <f>IF(종목!A25="","",종목!A25)</f>
+        <v/>
+      </c>
+      <c r="B25" s="11" t="str">
+        <f>IF(종목!B25="","",종목!B25)</f>
+        <v/>
+      </c>
+      <c r="C25" s="11" t="str">
+        <f>IF(종목!$A25="","",IF(종목!G25="","상장/정지",IF(종목!G25=0,"폐지(-100%)",IF(OR(종목!F25="",종목!F25=0),"신규상장",IFERROR(TEXT(종목!G25/종목!F25-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D25" s="11" t="str">
+        <f>IF(종목!$A25="","",IF(종목!H25="","상장/정지",IF(종목!H25=0,"폐지(-100%)",IF(OR(종목!G25="",종목!G25=0),"신규상장",IFERROR(TEXT(종목!H25/종목!G25-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="11" t="str">
+        <f>IF(종목!$A25="","",IF(종목!I25="","상장/정지",IF(종목!I25=0,"폐지(-100%)",IF(OR(종목!H25="",종목!H25=0),"신규상장",IFERROR(TEXT(종목!I25/종목!H25-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F25" s="11" t="str">
+        <f>IF(종목!$A25="","",IF(종목!J25="","상장/정지",IF(종목!J25=0,"폐지(-100%)",IF(OR(종목!I25="",종목!I25=0),"신규상장",IFERROR(TEXT(종목!J25/종목!I25-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11" t="str">
+        <f>IF(종목!$A25="","",IF(종목!K25="","상장/정지",IF(종목!K25=0,"폐지(-100%)",IF(OR(종목!J25="",종목!J25=0),"신규상장",IFERROR(TEXT(종목!K25/종목!J25-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="str">
+        <f>IF(종목!A26="","",종목!A26)</f>
+        <v/>
+      </c>
+      <c r="B26" s="11" t="str">
+        <f>IF(종목!B26="","",종목!B26)</f>
+        <v/>
+      </c>
+      <c r="C26" s="11" t="str">
+        <f>IF(종목!$A26="","",IF(종목!G26="","상장/정지",IF(종목!G26=0,"폐지(-100%)",IF(OR(종목!F26="",종목!F26=0),"신규상장",IFERROR(TEXT(종목!G26/종목!F26-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D26" s="11" t="str">
+        <f>IF(종목!$A26="","",IF(종목!H26="","상장/정지",IF(종목!H26=0,"폐지(-100%)",IF(OR(종목!G26="",종목!G26=0),"신규상장",IFERROR(TEXT(종목!H26/종목!G26-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E26" s="11" t="str">
+        <f>IF(종목!$A26="","",IF(종목!I26="","상장/정지",IF(종목!I26=0,"폐지(-100%)",IF(OR(종목!H26="",종목!H26=0),"신규상장",IFERROR(TEXT(종목!I26/종목!H26-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F26" s="11" t="str">
+        <f>IF(종목!$A26="","",IF(종목!J26="","상장/정지",IF(종목!J26=0,"폐지(-100%)",IF(OR(종목!I26="",종목!I26=0),"신규상장",IFERROR(TEXT(종목!J26/종목!I26-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G26" s="11" t="str">
+        <f>IF(종목!$A26="","",IF(종목!K26="","상장/정지",IF(종목!K26=0,"폐지(-100%)",IF(OR(종목!J26="",종목!J26=0),"신규상장",IFERROR(TEXT(종목!K26/종목!J26-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="str">
+        <f>IF(종목!A27="","",종목!A27)</f>
+        <v/>
+      </c>
+      <c r="B27" s="11" t="str">
+        <f>IF(종목!B27="","",종목!B27)</f>
+        <v/>
+      </c>
+      <c r="C27" s="11" t="str">
+        <f>IF(종목!$A27="","",IF(종목!G27="","상장/정지",IF(종목!G27=0,"폐지(-100%)",IF(OR(종목!F27="",종목!F27=0),"신규상장",IFERROR(TEXT(종목!G27/종목!F27-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D27" s="11" t="str">
+        <f>IF(종목!$A27="","",IF(종목!H27="","상장/정지",IF(종목!H27=0,"폐지(-100%)",IF(OR(종목!G27="",종목!G27=0),"신규상장",IFERROR(TEXT(종목!H27/종목!G27-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E27" s="11" t="str">
+        <f>IF(종목!$A27="","",IF(종목!I27="","상장/정지",IF(종목!I27=0,"폐지(-100%)",IF(OR(종목!H27="",종목!H27=0),"신규상장",IFERROR(TEXT(종목!I27/종목!H27-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F27" s="11" t="str">
+        <f>IF(종목!$A27="","",IF(종목!J27="","상장/정지",IF(종목!J27=0,"폐지(-100%)",IF(OR(종목!I27="",종목!I27=0),"신규상장",IFERROR(TEXT(종목!J27/종목!I27-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G27" s="11" t="str">
+        <f>IF(종목!$A27="","",IF(종목!K27="","상장/정지",IF(종목!K27=0,"폐지(-100%)",IF(OR(종목!J27="",종목!J27=0),"신규상장",IFERROR(TEXT(종목!K27/종목!J27-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="str">
+        <f>IF(종목!A28="","",종목!A28)</f>
+        <v/>
+      </c>
+      <c r="B28" s="11" t="str">
+        <f>IF(종목!B28="","",종목!B28)</f>
+        <v/>
+      </c>
+      <c r="C28" s="11" t="str">
+        <f>IF(종목!$A28="","",IF(종목!G28="","상장/정지",IF(종목!G28=0,"폐지(-100%)",IF(OR(종목!F28="",종목!F28=0),"신규상장",IFERROR(TEXT(종목!G28/종목!F28-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D28" s="11" t="str">
+        <f>IF(종목!$A28="","",IF(종목!H28="","상장/정지",IF(종목!H28=0,"폐지(-100%)",IF(OR(종목!G28="",종목!G28=0),"신규상장",IFERROR(TEXT(종목!H28/종목!G28-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="11" t="str">
+        <f>IF(종목!$A28="","",IF(종목!I28="","상장/정지",IF(종목!I28=0,"폐지(-100%)",IF(OR(종목!H28="",종목!H28=0),"신규상장",IFERROR(TEXT(종목!I28/종목!H28-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F28" s="11" t="str">
+        <f>IF(종목!$A28="","",IF(종목!J28="","상장/정지",IF(종목!J28=0,"폐지(-100%)",IF(OR(종목!I28="",종목!I28=0),"신규상장",IFERROR(TEXT(종목!J28/종목!I28-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G28" s="11" t="str">
+        <f>IF(종목!$A28="","",IF(종목!K28="","상장/정지",IF(종목!K28=0,"폐지(-100%)",IF(OR(종목!J28="",종목!J28=0),"신규상장",IFERROR(TEXT(종목!K28/종목!J28-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="str">
+        <f>IF(종목!A29="","",종목!A29)</f>
+        <v/>
+      </c>
+      <c r="B29" s="11" t="str">
+        <f>IF(종목!B29="","",종목!B29)</f>
+        <v/>
+      </c>
+      <c r="C29" s="11" t="str">
+        <f>IF(종목!$A29="","",IF(종목!G29="","상장/정지",IF(종목!G29=0,"폐지(-100%)",IF(OR(종목!F29="",종목!F29=0),"신규상장",IFERROR(TEXT(종목!G29/종목!F29-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D29" s="11" t="str">
+        <f>IF(종목!$A29="","",IF(종목!H29="","상장/정지",IF(종목!H29=0,"폐지(-100%)",IF(OR(종목!G29="",종목!G29=0),"신규상장",IFERROR(TEXT(종목!H29/종목!G29-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="11" t="str">
+        <f>IF(종목!$A29="","",IF(종목!I29="","상장/정지",IF(종목!I29=0,"폐지(-100%)",IF(OR(종목!H29="",종목!H29=0),"신규상장",IFERROR(TEXT(종목!I29/종목!H29-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F29" s="11" t="str">
+        <f>IF(종목!$A29="","",IF(종목!J29="","상장/정지",IF(종목!J29=0,"폐지(-100%)",IF(OR(종목!I29="",종목!I29=0),"신규상장",IFERROR(TEXT(종목!J29/종목!I29-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G29" s="11" t="str">
+        <f>IF(종목!$A29="","",IF(종목!K29="","상장/정지",IF(종목!K29=0,"폐지(-100%)",IF(OR(종목!J29="",종목!J29=0),"신규상장",IFERROR(TEXT(종목!K29/종목!J29-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="str">
+        <f>IF(종목!A30="","",종목!A30)</f>
+        <v/>
+      </c>
+      <c r="B30" s="11" t="str">
+        <f>IF(종목!B30="","",종목!B30)</f>
+        <v/>
+      </c>
+      <c r="C30" s="11" t="str">
+        <f>IF(종목!$A30="","",IF(종목!G30="","상장/정지",IF(종목!G30=0,"폐지(-100%)",IF(OR(종목!F30="",종목!F30=0),"신규상장",IFERROR(TEXT(종목!G30/종목!F30-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D30" s="11" t="str">
+        <f>IF(종목!$A30="","",IF(종목!H30="","상장/정지",IF(종목!H30=0,"폐지(-100%)",IF(OR(종목!G30="",종목!G30=0),"신규상장",IFERROR(TEXT(종목!H30/종목!G30-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E30" s="11" t="str">
+        <f>IF(종목!$A30="","",IF(종목!I30="","상장/정지",IF(종목!I30=0,"폐지(-100%)",IF(OR(종목!H30="",종목!H30=0),"신규상장",IFERROR(TEXT(종목!I30/종목!H30-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F30" s="11" t="str">
+        <f>IF(종목!$A30="","",IF(종목!J30="","상장/정지",IF(종목!J30=0,"폐지(-100%)",IF(OR(종목!I30="",종목!I30=0),"신규상장",IFERROR(TEXT(종목!J30/종목!I30-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11" t="str">
+        <f>IF(종목!$A30="","",IF(종목!K30="","상장/정지",IF(종목!K30=0,"폐지(-100%)",IF(OR(종목!J30="",종목!J30=0),"신규상장",IFERROR(TEXT(종목!K30/종목!J30-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="str">
+        <f>IF(종목!A31="","",종목!A31)</f>
+        <v/>
+      </c>
+      <c r="B31" s="11" t="str">
+        <f>IF(종목!B31="","",종목!B31)</f>
+        <v/>
+      </c>
+      <c r="C31" s="11" t="str">
+        <f>IF(종목!$A31="","",IF(종목!G31="","상장/정지",IF(종목!G31=0,"폐지(-100%)",IF(OR(종목!F31="",종목!F31=0),"신규상장",IFERROR(TEXT(종목!G31/종목!F31-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D31" s="11" t="str">
+        <f>IF(종목!$A31="","",IF(종목!H31="","상장/정지",IF(종목!H31=0,"폐지(-100%)",IF(OR(종목!G31="",종목!G31=0),"신규상장",IFERROR(TEXT(종목!H31/종목!G31-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E31" s="11" t="str">
+        <f>IF(종목!$A31="","",IF(종목!I31="","상장/정지",IF(종목!I31=0,"폐지(-100%)",IF(OR(종목!H31="",종목!H31=0),"신규상장",IFERROR(TEXT(종목!I31/종목!H31-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F31" s="11" t="str">
+        <f>IF(종목!$A31="","",IF(종목!J31="","상장/정지",IF(종목!J31=0,"폐지(-100%)",IF(OR(종목!I31="",종목!I31=0),"신규상장",IFERROR(TEXT(종목!J31/종목!I31-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G31" s="11" t="str">
+        <f>IF(종목!$A31="","",IF(종목!K31="","상장/정지",IF(종목!K31=0,"폐지(-100%)",IF(OR(종목!J31="",종목!J31=0),"신규상장",IFERROR(TEXT(종목!K31/종목!J31-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="str">
+        <f>IF(종목!A32="","",종목!A32)</f>
+        <v/>
+      </c>
+      <c r="B32" s="11" t="str">
+        <f>IF(종목!B32="","",종목!B32)</f>
+        <v/>
+      </c>
+      <c r="C32" s="11" t="str">
+        <f>IF(종목!$A32="","",IF(종목!G32="","상장/정지",IF(종목!G32=0,"폐지(-100%)",IF(OR(종목!F32="",종목!F32=0),"신규상장",IFERROR(TEXT(종목!G32/종목!F32-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D32" s="11" t="str">
+        <f>IF(종목!$A32="","",IF(종목!H32="","상장/정지",IF(종목!H32=0,"폐지(-100%)",IF(OR(종목!G32="",종목!G32=0),"신규상장",IFERROR(TEXT(종목!H32/종목!G32-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="11" t="str">
+        <f>IF(종목!$A32="","",IF(종목!I32="","상장/정지",IF(종목!I32=0,"폐지(-100%)",IF(OR(종목!H32="",종목!H32=0),"신규상장",IFERROR(TEXT(종목!I32/종목!H32-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F32" s="11" t="str">
+        <f>IF(종목!$A32="","",IF(종목!J32="","상장/정지",IF(종목!J32=0,"폐지(-100%)",IF(OR(종목!I32="",종목!I32=0),"신규상장",IFERROR(TEXT(종목!J32/종목!I32-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G32" s="11" t="str">
+        <f>IF(종목!$A32="","",IF(종목!K32="","상장/정지",IF(종목!K32=0,"폐지(-100%)",IF(OR(종목!J32="",종목!J32=0),"신규상장",IFERROR(TEXT(종목!K32/종목!J32-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="str">
+        <f>IF(종목!A33="","",종목!A33)</f>
+        <v/>
+      </c>
+      <c r="B33" s="11" t="str">
+        <f>IF(종목!B33="","",종목!B33)</f>
+        <v/>
+      </c>
+      <c r="C33" s="11" t="str">
+        <f>IF(종목!$A33="","",IF(종목!G33="","상장/정지",IF(종목!G33=0,"폐지(-100%)",IF(OR(종목!F33="",종목!F33=0),"신규상장",IFERROR(TEXT(종목!G33/종목!F33-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D33" s="11" t="str">
+        <f>IF(종목!$A33="","",IF(종목!H33="","상장/정지",IF(종목!H33=0,"폐지(-100%)",IF(OR(종목!G33="",종목!G33=0),"신규상장",IFERROR(TEXT(종목!H33/종목!G33-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="11" t="str">
+        <f>IF(종목!$A33="","",IF(종목!I33="","상장/정지",IF(종목!I33=0,"폐지(-100%)",IF(OR(종목!H33="",종목!H33=0),"신규상장",IFERROR(TEXT(종목!I33/종목!H33-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F33" s="11" t="str">
+        <f>IF(종목!$A33="","",IF(종목!J33="","상장/정지",IF(종목!J33=0,"폐지(-100%)",IF(OR(종목!I33="",종목!I33=0),"신규상장",IFERROR(TEXT(종목!J33/종목!I33-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G33" s="11" t="str">
+        <f>IF(종목!$A33="","",IF(종목!K33="","상장/정지",IF(종목!K33=0,"폐지(-100%)",IF(OR(종목!J33="",종목!J33=0),"신규상장",IFERROR(TEXT(종목!K33/종목!J33-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="str">
+        <f>IF(종목!A34="","",종목!A34)</f>
+        <v/>
+      </c>
+      <c r="B34" s="11" t="str">
+        <f>IF(종목!B34="","",종목!B34)</f>
+        <v/>
+      </c>
+      <c r="C34" s="11" t="str">
+        <f>IF(종목!$A34="","",IF(종목!G34="","상장/정지",IF(종목!G34=0,"폐지(-100%)",IF(OR(종목!F34="",종목!F34=0),"신규상장",IFERROR(TEXT(종목!G34/종목!F34-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D34" s="11" t="str">
+        <f>IF(종목!$A34="","",IF(종목!H34="","상장/정지",IF(종목!H34=0,"폐지(-100%)",IF(OR(종목!G34="",종목!G34=0),"신규상장",IFERROR(TEXT(종목!H34/종목!G34-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E34" s="11" t="str">
+        <f>IF(종목!$A34="","",IF(종목!I34="","상장/정지",IF(종목!I34=0,"폐지(-100%)",IF(OR(종목!H34="",종목!H34=0),"신규상장",IFERROR(TEXT(종목!I34/종목!H34-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F34" s="11" t="str">
+        <f>IF(종목!$A34="","",IF(종목!J34="","상장/정지",IF(종목!J34=0,"폐지(-100%)",IF(OR(종목!I34="",종목!I34=0),"신규상장",IFERROR(TEXT(종목!J34/종목!I34-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G34" s="11" t="str">
+        <f>IF(종목!$A34="","",IF(종목!K34="","상장/정지",IF(종목!K34=0,"폐지(-100%)",IF(OR(종목!J34="",종목!J34=0),"신규상장",IFERROR(TEXT(종목!K34/종목!J34-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="str">
+        <f>IF(종목!A35="","",종목!A35)</f>
+        <v/>
+      </c>
+      <c r="B35" s="11" t="str">
+        <f>IF(종목!B35="","",종목!B35)</f>
+        <v/>
+      </c>
+      <c r="C35" s="11" t="str">
+        <f>IF(종목!$A35="","",IF(종목!G35="","상장/정지",IF(종목!G35=0,"폐지(-100%)",IF(OR(종목!F35="",종목!F35=0),"신규상장",IFERROR(TEXT(종목!G35/종목!F35-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D35" s="11" t="str">
+        <f>IF(종목!$A35="","",IF(종목!H35="","상장/정지",IF(종목!H35=0,"폐지(-100%)",IF(OR(종목!G35="",종목!G35=0),"신규상장",IFERROR(TEXT(종목!H35/종목!G35-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E35" s="11" t="str">
+        <f>IF(종목!$A35="","",IF(종목!I35="","상장/정지",IF(종목!I35=0,"폐지(-100%)",IF(OR(종목!H35="",종목!H35=0),"신규상장",IFERROR(TEXT(종목!I35/종목!H35-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F35" s="11" t="str">
+        <f>IF(종목!$A35="","",IF(종목!J35="","상장/정지",IF(종목!J35=0,"폐지(-100%)",IF(OR(종목!I35="",종목!I35=0),"신규상장",IFERROR(TEXT(종목!J35/종목!I35-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11" t="str">
+        <f>IF(종목!$A35="","",IF(종목!K35="","상장/정지",IF(종목!K35=0,"폐지(-100%)",IF(OR(종목!J35="",종목!J35=0),"신규상장",IFERROR(TEXT(종목!K35/종목!J35-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="str">
+        <f>IF(종목!A36="","",종목!A36)</f>
+        <v/>
+      </c>
+      <c r="B36" s="11" t="str">
+        <f>IF(종목!B36="","",종목!B36)</f>
+        <v/>
+      </c>
+      <c r="C36" s="11" t="str">
+        <f>IF(종목!$A36="","",IF(종목!G36="","상장/정지",IF(종목!G36=0,"폐지(-100%)",IF(OR(종목!F36="",종목!F36=0),"신규상장",IFERROR(TEXT(종목!G36/종목!F36-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D36" s="11" t="str">
+        <f>IF(종목!$A36="","",IF(종목!H36="","상장/정지",IF(종목!H36=0,"폐지(-100%)",IF(OR(종목!G36="",종목!G36=0),"신규상장",IFERROR(TEXT(종목!H36/종목!G36-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E36" s="11" t="str">
+        <f>IF(종목!$A36="","",IF(종목!I36="","상장/정지",IF(종목!I36=0,"폐지(-100%)",IF(OR(종목!H36="",종목!H36=0),"신규상장",IFERROR(TEXT(종목!I36/종목!H36-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F36" s="11" t="str">
+        <f>IF(종목!$A36="","",IF(종목!J36="","상장/정지",IF(종목!J36=0,"폐지(-100%)",IF(OR(종목!I36="",종목!I36=0),"신규상장",IFERROR(TEXT(종목!J36/종목!I36-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G36" s="11" t="str">
+        <f>IF(종목!$A36="","",IF(종목!K36="","상장/정지",IF(종목!K36=0,"폐지(-100%)",IF(OR(종목!J36="",종목!J36=0),"신규상장",IFERROR(TEXT(종목!K36/종목!J36-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="str">
+        <f>IF(종목!A37="","",종목!A37)</f>
+        <v/>
+      </c>
+      <c r="B37" s="11" t="str">
+        <f>IF(종목!B37="","",종목!B37)</f>
+        <v/>
+      </c>
+      <c r="C37" s="11" t="str">
+        <f>IF(종목!$A37="","",IF(종목!G37="","상장/정지",IF(종목!G37=0,"폐지(-100%)",IF(OR(종목!F37="",종목!F37=0),"신규상장",IFERROR(TEXT(종목!G37/종목!F37-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D37" s="11" t="str">
+        <f>IF(종목!$A37="","",IF(종목!H37="","상장/정지",IF(종목!H37=0,"폐지(-100%)",IF(OR(종목!G37="",종목!G37=0),"신규상장",IFERROR(TEXT(종목!H37/종목!G37-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E37" s="11" t="str">
+        <f>IF(종목!$A37="","",IF(종목!I37="","상장/정지",IF(종목!I37=0,"폐지(-100%)",IF(OR(종목!H37="",종목!H37=0),"신규상장",IFERROR(TEXT(종목!I37/종목!H37-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F37" s="11" t="str">
+        <f>IF(종목!$A37="","",IF(종목!J37="","상장/정지",IF(종목!J37=0,"폐지(-100%)",IF(OR(종목!I37="",종목!I37=0),"신규상장",IFERROR(TEXT(종목!J37/종목!I37-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G37" s="11" t="str">
+        <f>IF(종목!$A37="","",IF(종목!K37="","상장/정지",IF(종목!K37=0,"폐지(-100%)",IF(OR(종목!J37="",종목!J37=0),"신규상장",IFERROR(TEXT(종목!K37/종목!J37-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="str">
+        <f>IF(종목!A38="","",종목!A38)</f>
+        <v/>
+      </c>
+      <c r="B38" s="11" t="str">
+        <f>IF(종목!B38="","",종목!B38)</f>
+        <v/>
+      </c>
+      <c r="C38" s="11" t="str">
+        <f>IF(종목!$A38="","",IF(종목!G38="","상장/정지",IF(종목!G38=0,"폐지(-100%)",IF(OR(종목!F38="",종목!F38=0),"신규상장",IFERROR(TEXT(종목!G38/종목!F38-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D38" s="11" t="str">
+        <f>IF(종목!$A38="","",IF(종목!H38="","상장/정지",IF(종목!H38=0,"폐지(-100%)",IF(OR(종목!G38="",종목!G38=0),"신규상장",IFERROR(TEXT(종목!H38/종목!G38-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E38" s="11" t="str">
+        <f>IF(종목!$A38="","",IF(종목!I38="","상장/정지",IF(종목!I38=0,"폐지(-100%)",IF(OR(종목!H38="",종목!H38=0),"신규상장",IFERROR(TEXT(종목!I38/종목!H38-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F38" s="11" t="str">
+        <f>IF(종목!$A38="","",IF(종목!J38="","상장/정지",IF(종목!J38=0,"폐지(-100%)",IF(OR(종목!I38="",종목!I38=0),"신규상장",IFERROR(TEXT(종목!J38/종목!I38-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G38" s="11" t="str">
+        <f>IF(종목!$A38="","",IF(종목!K38="","상장/정지",IF(종목!K38=0,"폐지(-100%)",IF(OR(종목!J38="",종목!J38=0),"신규상장",IFERROR(TEXT(종목!K38/종목!J38-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="str">
+        <f>IF(종목!A39="","",종목!A39)</f>
+        <v/>
+      </c>
+      <c r="B39" s="11" t="str">
+        <f>IF(종목!B39="","",종목!B39)</f>
+        <v/>
+      </c>
+      <c r="C39" s="11" t="str">
+        <f>IF(종목!$A39="","",IF(종목!G39="","상장/정지",IF(종목!G39=0,"폐지(-100%)",IF(OR(종목!F39="",종목!F39=0),"신규상장",IFERROR(TEXT(종목!G39/종목!F39-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D39" s="11" t="str">
+        <f>IF(종목!$A39="","",IF(종목!H39="","상장/정지",IF(종목!H39=0,"폐지(-100%)",IF(OR(종목!G39="",종목!G39=0),"신규상장",IFERROR(TEXT(종목!H39/종목!G39-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E39" s="11" t="str">
+        <f>IF(종목!$A39="","",IF(종목!I39="","상장/정지",IF(종목!I39=0,"폐지(-100%)",IF(OR(종목!H39="",종목!H39=0),"신규상장",IFERROR(TEXT(종목!I39/종목!H39-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F39" s="11" t="str">
+        <f>IF(종목!$A39="","",IF(종목!J39="","상장/정지",IF(종목!J39=0,"폐지(-100%)",IF(OR(종목!I39="",종목!I39=0),"신규상장",IFERROR(TEXT(종목!J39/종목!I39-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G39" s="11" t="str">
+        <f>IF(종목!$A39="","",IF(종목!K39="","상장/정지",IF(종목!K39=0,"폐지(-100%)",IF(OR(종목!J39="",종목!J39=0),"신규상장",IFERROR(TEXT(종목!K39/종목!J39-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="str">
+        <f>IF(종목!A40="","",종목!A40)</f>
+        <v/>
+      </c>
+      <c r="B40" s="11" t="str">
+        <f>IF(종목!B40="","",종목!B40)</f>
+        <v/>
+      </c>
+      <c r="C40" s="11" t="str">
+        <f>IF(종목!$A40="","",IF(종목!G40="","상장/정지",IF(종목!G40=0,"폐지(-100%)",IF(OR(종목!F40="",종목!F40=0),"신규상장",IFERROR(TEXT(종목!G40/종목!F40-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D40" s="11" t="str">
+        <f>IF(종목!$A40="","",IF(종목!H40="","상장/정지",IF(종목!H40=0,"폐지(-100%)",IF(OR(종목!G40="",종목!G40=0),"신규상장",IFERROR(TEXT(종목!H40/종목!G40-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E40" s="11" t="str">
+        <f>IF(종목!$A40="","",IF(종목!I40="","상장/정지",IF(종목!I40=0,"폐지(-100%)",IF(OR(종목!H40="",종목!H40=0),"신규상장",IFERROR(TEXT(종목!I40/종목!H40-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F40" s="11" t="str">
+        <f>IF(종목!$A40="","",IF(종목!J40="","상장/정지",IF(종목!J40=0,"폐지(-100%)",IF(OR(종목!I40="",종목!I40=0),"신규상장",IFERROR(TEXT(종목!J40/종목!I40-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G40" s="11" t="str">
+        <f>IF(종목!$A40="","",IF(종목!K40="","상장/정지",IF(종목!K40=0,"폐지(-100%)",IF(OR(종목!J40="",종목!J40=0),"신규상장",IFERROR(TEXT(종목!K40/종목!J40-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="str">
+        <f>IF(종목!A41="","",종목!A41)</f>
+        <v/>
+      </c>
+      <c r="B41" s="11" t="str">
+        <f>IF(종목!B41="","",종목!B41)</f>
+        <v/>
+      </c>
+      <c r="C41" s="11" t="str">
+        <f>IF(종목!$A41="","",IF(종목!G41="","상장/정지",IF(종목!G41=0,"폐지(-100%)",IF(OR(종목!F41="",종목!F41=0),"신규상장",IFERROR(TEXT(종목!G41/종목!F41-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D41" s="11" t="str">
+        <f>IF(종목!$A41="","",IF(종목!H41="","상장/정지",IF(종목!H41=0,"폐지(-100%)",IF(OR(종목!G41="",종목!G41=0),"신규상장",IFERROR(TEXT(종목!H41/종목!G41-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E41" s="11" t="str">
+        <f>IF(종목!$A41="","",IF(종목!I41="","상장/정지",IF(종목!I41=0,"폐지(-100%)",IF(OR(종목!H41="",종목!H41=0),"신규상장",IFERROR(TEXT(종목!I41/종목!H41-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F41" s="11" t="str">
+        <f>IF(종목!$A41="","",IF(종목!J41="","상장/정지",IF(종목!J41=0,"폐지(-100%)",IF(OR(종목!I41="",종목!I41=0),"신규상장",IFERROR(TEXT(종목!J41/종목!I41-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G41" s="11" t="str">
+        <f>IF(종목!$A41="","",IF(종목!K41="","상장/정지",IF(종목!K41=0,"폐지(-100%)",IF(OR(종목!J41="",종목!J41=0),"신규상장",IFERROR(TEXT(종목!K41/종목!J41-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="str">
+        <f>IF(종목!A42="","",종목!A42)</f>
+        <v/>
+      </c>
+      <c r="B42" s="11" t="str">
+        <f>IF(종목!B42="","",종목!B42)</f>
+        <v/>
+      </c>
+      <c r="C42" s="11" t="str">
+        <f>IF(종목!$A42="","",IF(종목!G42="","상장/정지",IF(종목!G42=0,"폐지(-100%)",IF(OR(종목!F42="",종목!F42=0),"신규상장",IFERROR(TEXT(종목!G42/종목!F42-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D42" s="11" t="str">
+        <f>IF(종목!$A42="","",IF(종목!H42="","상장/정지",IF(종목!H42=0,"폐지(-100%)",IF(OR(종목!G42="",종목!G42=0),"신규상장",IFERROR(TEXT(종목!H42/종목!G42-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E42" s="11" t="str">
+        <f>IF(종목!$A42="","",IF(종목!I42="","상장/정지",IF(종목!I42=0,"폐지(-100%)",IF(OR(종목!H42="",종목!H42=0),"신규상장",IFERROR(TEXT(종목!I42/종목!H42-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F42" s="11" t="str">
+        <f>IF(종목!$A42="","",IF(종목!J42="","상장/정지",IF(종목!J42=0,"폐지(-100%)",IF(OR(종목!I42="",종목!I42=0),"신규상장",IFERROR(TEXT(종목!J42/종목!I42-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G42" s="11" t="str">
+        <f>IF(종목!$A42="","",IF(종목!K42="","상장/정지",IF(종목!K42=0,"폐지(-100%)",IF(OR(종목!J42="",종목!J42=0),"신규상장",IFERROR(TEXT(종목!K42/종목!J42-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="str">
+        <f>IF(종목!A43="","",종목!A43)</f>
+        <v/>
+      </c>
+      <c r="B43" s="11" t="str">
+        <f>IF(종목!B43="","",종목!B43)</f>
+        <v/>
+      </c>
+      <c r="C43" s="11" t="str">
+        <f>IF(종목!$A43="","",IF(종목!G43="","상장/정지",IF(종목!G43=0,"폐지(-100%)",IF(OR(종목!F43="",종목!F43=0),"신규상장",IFERROR(TEXT(종목!G43/종목!F43-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D43" s="11" t="str">
+        <f>IF(종목!$A43="","",IF(종목!H43="","상장/정지",IF(종목!H43=0,"폐지(-100%)",IF(OR(종목!G43="",종목!G43=0),"신규상장",IFERROR(TEXT(종목!H43/종목!G43-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E43" s="11" t="str">
+        <f>IF(종목!$A43="","",IF(종목!I43="","상장/정지",IF(종목!I43=0,"폐지(-100%)",IF(OR(종목!H43="",종목!H43=0),"신규상장",IFERROR(TEXT(종목!I43/종목!H43-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F43" s="11" t="str">
+        <f>IF(종목!$A43="","",IF(종목!J43="","상장/정지",IF(종목!J43=0,"폐지(-100%)",IF(OR(종목!I43="",종목!I43=0),"신규상장",IFERROR(TEXT(종목!J43/종목!I43-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11" t="str">
+        <f>IF(종목!$A43="","",IF(종목!K43="","상장/정지",IF(종목!K43=0,"폐지(-100%)",IF(OR(종목!J43="",종목!J43=0),"신규상장",IFERROR(TEXT(종목!K43/종목!J43-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="str">
+        <f>IF(종목!A44="","",종목!A44)</f>
+        <v/>
+      </c>
+      <c r="B44" s="11" t="str">
+        <f>IF(종목!B44="","",종목!B44)</f>
+        <v/>
+      </c>
+      <c r="C44" s="11" t="str">
+        <f>IF(종목!$A44="","",IF(종목!G44="","상장/정지",IF(종목!G44=0,"폐지(-100%)",IF(OR(종목!F44="",종목!F44=0),"신규상장",IFERROR(TEXT(종목!G44/종목!F44-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D44" s="11" t="str">
+        <f>IF(종목!$A44="","",IF(종목!H44="","상장/정지",IF(종목!H44=0,"폐지(-100%)",IF(OR(종목!G44="",종목!G44=0),"신규상장",IFERROR(TEXT(종목!H44/종목!G44-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E44" s="11" t="str">
+        <f>IF(종목!$A44="","",IF(종목!I44="","상장/정지",IF(종목!I44=0,"폐지(-100%)",IF(OR(종목!H44="",종목!H44=0),"신규상장",IFERROR(TEXT(종목!I44/종목!H44-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F44" s="11" t="str">
+        <f>IF(종목!$A44="","",IF(종목!J44="","상장/정지",IF(종목!J44=0,"폐지(-100%)",IF(OR(종목!I44="",종목!I44=0),"신규상장",IFERROR(TEXT(종목!J44/종목!I44-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G44" s="11" t="str">
+        <f>IF(종목!$A44="","",IF(종목!K44="","상장/정지",IF(종목!K44=0,"폐지(-100%)",IF(OR(종목!J44="",종목!J44=0),"신규상장",IFERROR(TEXT(종목!K44/종목!J44-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="str">
+        <f>IF(종목!A45="","",종목!A45)</f>
+        <v/>
+      </c>
+      <c r="B45" s="11" t="str">
+        <f>IF(종목!B45="","",종목!B45)</f>
+        <v/>
+      </c>
+      <c r="C45" s="11" t="str">
+        <f>IF(종목!$A45="","",IF(종목!G45="","상장/정지",IF(종목!G45=0,"폐지(-100%)",IF(OR(종목!F45="",종목!F45=0),"신규상장",IFERROR(TEXT(종목!G45/종목!F45-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D45" s="11" t="str">
+        <f>IF(종목!$A45="","",IF(종목!H45="","상장/정지",IF(종목!H45=0,"폐지(-100%)",IF(OR(종목!G45="",종목!G45=0),"신규상장",IFERROR(TEXT(종목!H45/종목!G45-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="11" t="str">
+        <f>IF(종목!$A45="","",IF(종목!I45="","상장/정지",IF(종목!I45=0,"폐지(-100%)",IF(OR(종목!H45="",종목!H45=0),"신규상장",IFERROR(TEXT(종목!I45/종목!H45-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F45" s="11" t="str">
+        <f>IF(종목!$A45="","",IF(종목!J45="","상장/정지",IF(종목!J45=0,"폐지(-100%)",IF(OR(종목!I45="",종목!I45=0),"신규상장",IFERROR(TEXT(종목!J45/종목!I45-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11" t="str">
+        <f>IF(종목!$A45="","",IF(종목!K45="","상장/정지",IF(종목!K45=0,"폐지(-100%)",IF(OR(종목!J45="",종목!J45=0),"신규상장",IFERROR(TEXT(종목!K45/종목!J45-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="str">
+        <f>IF(종목!A46="","",종목!A46)</f>
+        <v/>
+      </c>
+      <c r="B46" s="11" t="str">
+        <f>IF(종목!B46="","",종목!B46)</f>
+        <v/>
+      </c>
+      <c r="C46" s="11" t="str">
+        <f>IF(종목!$A46="","",IF(종목!G46="","상장/정지",IF(종목!G46=0,"폐지(-100%)",IF(OR(종목!F46="",종목!F46=0),"신규상장",IFERROR(TEXT(종목!G46/종목!F46-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D46" s="11" t="str">
+        <f>IF(종목!$A46="","",IF(종목!H46="","상장/정지",IF(종목!H46=0,"폐지(-100%)",IF(OR(종목!G46="",종목!G46=0),"신규상장",IFERROR(TEXT(종목!H46/종목!G46-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E46" s="11" t="str">
+        <f>IF(종목!$A46="","",IF(종목!I46="","상장/정지",IF(종목!I46=0,"폐지(-100%)",IF(OR(종목!H46="",종목!H46=0),"신규상장",IFERROR(TEXT(종목!I46/종목!H46-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F46" s="11" t="str">
+        <f>IF(종목!$A46="","",IF(종목!J46="","상장/정지",IF(종목!J46=0,"폐지(-100%)",IF(OR(종목!I46="",종목!I46=0),"신규상장",IFERROR(TEXT(종목!J46/종목!I46-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11" t="str">
+        <f>IF(종목!$A46="","",IF(종목!K46="","상장/정지",IF(종목!K46=0,"폐지(-100%)",IF(OR(종목!J46="",종목!J46=0),"신규상장",IFERROR(TEXT(종목!K46/종목!J46-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="str">
+        <f>IF(종목!A47="","",종목!A47)</f>
+        <v/>
+      </c>
+      <c r="B47" s="11" t="str">
+        <f>IF(종목!B47="","",종목!B47)</f>
+        <v/>
+      </c>
+      <c r="C47" s="11" t="str">
+        <f>IF(종목!$A47="","",IF(종목!G47="","상장/정지",IF(종목!G47=0,"폐지(-100%)",IF(OR(종목!F47="",종목!F47=0),"신규상장",IFERROR(TEXT(종목!G47/종목!F47-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D47" s="11" t="str">
+        <f>IF(종목!$A47="","",IF(종목!H47="","상장/정지",IF(종목!H47=0,"폐지(-100%)",IF(OR(종목!G47="",종목!G47=0),"신규상장",IFERROR(TEXT(종목!H47/종목!G47-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E47" s="11" t="str">
+        <f>IF(종목!$A47="","",IF(종목!I47="","상장/정지",IF(종목!I47=0,"폐지(-100%)",IF(OR(종목!H47="",종목!H47=0),"신규상장",IFERROR(TEXT(종목!I47/종목!H47-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F47" s="11" t="str">
+        <f>IF(종목!$A47="","",IF(종목!J47="","상장/정지",IF(종목!J47=0,"폐지(-100%)",IF(OR(종목!I47="",종목!I47=0),"신규상장",IFERROR(TEXT(종목!J47/종목!I47-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11" t="str">
+        <f>IF(종목!$A47="","",IF(종목!K47="","상장/정지",IF(종목!K47=0,"폐지(-100%)",IF(OR(종목!J47="",종목!J47=0),"신규상장",IFERROR(TEXT(종목!K47/종목!J47-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="str">
+        <f>IF(종목!A48="","",종목!A48)</f>
+        <v/>
+      </c>
+      <c r="B48" s="11" t="str">
+        <f>IF(종목!B48="","",종목!B48)</f>
+        <v/>
+      </c>
+      <c r="C48" s="11" t="str">
+        <f>IF(종목!$A48="","",IF(종목!G48="","상장/정지",IF(종목!G48=0,"폐지(-100%)",IF(OR(종목!F48="",종목!F48=0),"신규상장",IFERROR(TEXT(종목!G48/종목!F48-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D48" s="11" t="str">
+        <f>IF(종목!$A48="","",IF(종목!H48="","상장/정지",IF(종목!H48=0,"폐지(-100%)",IF(OR(종목!G48="",종목!G48=0),"신규상장",IFERROR(TEXT(종목!H48/종목!G48-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E48" s="11" t="str">
+        <f>IF(종목!$A48="","",IF(종목!I48="","상장/정지",IF(종목!I48=0,"폐지(-100%)",IF(OR(종목!H48="",종목!H48=0),"신규상장",IFERROR(TEXT(종목!I48/종목!H48-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F48" s="11" t="str">
+        <f>IF(종목!$A48="","",IF(종목!J48="","상장/정지",IF(종목!J48=0,"폐지(-100%)",IF(OR(종목!I48="",종목!I48=0),"신규상장",IFERROR(TEXT(종목!J48/종목!I48-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11" t="str">
+        <f>IF(종목!$A48="","",IF(종목!K48="","상장/정지",IF(종목!K48=0,"폐지(-100%)",IF(OR(종목!J48="",종목!J48=0),"신규상장",IFERROR(TEXT(종목!K48/종목!J48-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="str">
+        <f>IF(종목!A49="","",종목!A49)</f>
+        <v/>
+      </c>
+      <c r="B49" s="11" t="str">
+        <f>IF(종목!B49="","",종목!B49)</f>
+        <v/>
+      </c>
+      <c r="C49" s="11" t="str">
+        <f>IF(종목!$A49="","",IF(종목!G49="","상장/정지",IF(종목!G49=0,"폐지(-100%)",IF(OR(종목!F49="",종목!F49=0),"신규상장",IFERROR(TEXT(종목!G49/종목!F49-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D49" s="11" t="str">
+        <f>IF(종목!$A49="","",IF(종목!H49="","상장/정지",IF(종목!H49=0,"폐지(-100%)",IF(OR(종목!G49="",종목!G49=0),"신규상장",IFERROR(TEXT(종목!H49/종목!G49-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E49" s="11" t="str">
+        <f>IF(종목!$A49="","",IF(종목!I49="","상장/정지",IF(종목!I49=0,"폐지(-100%)",IF(OR(종목!H49="",종목!H49=0),"신규상장",IFERROR(TEXT(종목!I49/종목!H49-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F49" s="11" t="str">
+        <f>IF(종목!$A49="","",IF(종목!J49="","상장/정지",IF(종목!J49=0,"폐지(-100%)",IF(OR(종목!I49="",종목!I49=0),"신규상장",IFERROR(TEXT(종목!J49/종목!I49-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11" t="str">
+        <f>IF(종목!$A49="","",IF(종목!K49="","상장/정지",IF(종목!K49=0,"폐지(-100%)",IF(OR(종목!J49="",종목!J49=0),"신규상장",IFERROR(TEXT(종목!K49/종목!J49-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="str">
+        <f>IF(종목!A50="","",종목!A50)</f>
+        <v/>
+      </c>
+      <c r="B50" s="11" t="str">
+        <f>IF(종목!B50="","",종목!B50)</f>
+        <v/>
+      </c>
+      <c r="C50" s="11" t="str">
+        <f>IF(종목!$A50="","",IF(종목!G50="","상장/정지",IF(종목!G50=0,"폐지(-100%)",IF(OR(종목!F50="",종목!F50=0),"신규상장",IFERROR(TEXT(종목!G50/종목!F50-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="D50" s="11" t="str">
+        <f>IF(종목!$A50="","",IF(종목!H50="","상장/정지",IF(종목!H50=0,"폐지(-100%)",IF(OR(종목!G50="",종목!G50=0),"신규상장",IFERROR(TEXT(종목!H50/종목!G50-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="E50" s="11" t="str">
+        <f>IF(종목!$A50="","",IF(종목!I50="","상장/정지",IF(종목!I50=0,"폐지(-100%)",IF(OR(종목!H50="",종목!H50=0),"신규상장",IFERROR(TEXT(종목!I50/종목!H50-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="F50" s="11" t="str">
+        <f>IF(종목!$A50="","",IF(종목!J50="","상장/정지",IF(종목!J50=0,"폐지(-100%)",IF(OR(종목!I50="",종목!I50=0),"신규상장",IFERROR(TEXT(종목!J50/종목!I50-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+      <c r="G50" s="11" t="str">
+        <f>IF(종목!$A50="","",IF(종목!K50="","상장/정지",IF(종목!K50=0,"폐지(-100%)",IF(OR(종목!J50="",종목!J50=0),"신규상장",IFERROR(TEXT(종목!K50/종목!J50-1,"+0%;-0%"),"—")))))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
